--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260813.xlsx
@@ -16,9 +16,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_会議体・意見聴取" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_課題・リスク" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_変更管理・打合せ記録" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_仕様書対応表" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$M$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$N$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -100,12 +101,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -173,7 +174,7 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1382,28 +1383,980 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>条項</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>仕様書の記載内容（原文）</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>対応する作業（01_WBS）</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>作業数</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>網羅</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>計画の考え方</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>本業務は、国や福島県の動向、本町の高齢者の状況を的確に把握し、高齢者へのアンケート調査結果及び小野町高齢者保健福祉計画・第9期介護保険事業計画の評価等を行い、本町が取り組むべき課題や高齢者保健福祉施策の方向性、サービスの目標量を定める（第10期計画）とする。</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>前提条項</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>計画の考え方</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>2(1)</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>令和9年度から令和11年度までの3年間に実施する取り組みを定める計画とする。</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>前提条項</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>計画の考え方</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>2(2)</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>国が示す第10期計画に関する基本的な考え方を踏まえた上で、本町の特性を活かした計画とする。</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>1-5 第3期地域福祉計画との役割分担の整理</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>計画の考え方</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2(3)</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>2-7 認知症高齢者の分析
+8-3 認知症施策推進基本計画の包含方針</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>計画の考え方</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>契約締結の日から令和9年3月31日まで</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>10-8 納品・検収</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>4(1)</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>基礎的な地域データ及び資料の整理分析（現状分析）。高齢者福祉・介護保険をめぐる施策の動向、小野町の概要及び社会経済的特性、地域福祉資源の整備状況、高齢者の現況動向及びサービスの利用状況等について、小野町が提供するデータをもとに整理分析を行う。（計画策定の検討資料として活用するため、各種事項の将来推計を行う。なお、推計にあたっては、可能な限り細分化する）</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>1-4 第9期計画本文の確認</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>4(1)①ア</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>統計分析（ア）人口</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>2-1 人口・世帯の分析
+2-2 第1号被保険者の分析</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>4(1)①イ</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>2-3 認定者数・認定率の分析
+2-4 認定者数の異常値の検証
+2-7 認知症高齢者の分析</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>4(1)①ウ</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>統計分析（ウ）居宅サービス・施設サービス・地域密着型サービスの受給者数</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>2-5 サービス受給者数の分析</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>4(1)①エ</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>統計分析（エ）介護予防事業対象者数</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>2-6 介護予防事業対象者数の分析</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>4(1)①オ</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>統計分析（オ）その他計画策定に必要な推計</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>2-8 サービス自給率の分析
+2-10 見える化 優先度C分野の出力</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>4(1)②</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>3-1 給付費等分析結果報告書の作成
+3-2 町の給付実績との突合
+5-1 協議会資料（第9期評価・調査結果）の作成
+5-2 成果目標の達成状況の確定
+5-3 施設整備方針との不整合の確認</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>4(1)③</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>4-1 調査結果報告書の確認
+4-2 集計データの整理
+4-3 集計結果・分析報告書の作成
+4-4 クロス集計の設計
+4-5 個票によるクロス集計</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>4(2)</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>2-9 介護保険財政の分析
+7-1 算定シートの構築
+7-2 保険料算定のケース設定の確定
+7-3 被保険者数・認定者数の推計
+7-4 サービス見込量の推計
+7-5 見える化システムへの入力作業
+7-6 保険料のケース別算定</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>4(3)</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>6-1 骨子案の作成
+6-2 骨子案の協議（協議会）
+8-1 素案の作成
+8-2 成果指標の目標値案の作成
+8-4 見込量・保険料・成果指標の反映
+8-5 素案の協議（協議会）</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>4(4)</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>最終調整及び計画書の作成・取りまとめ。（1）から（3）の結果を踏まえ、小野町高齢者保健福祉計画・第10期介護保険事業計画書を作成するものとする。</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>10-1 計画書の原稿確定</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>業務の内容</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>4(5)</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>5-1 協議会資料（第9期評価・調査結果）の作成
+6-2 骨子案の協議（協議会）
+8-5 素案の協議（協議会）
+9-1 協議会の開催回数・時期の確定
+9-2 協議会 第1回（第9期の評価・調査結果）
+9-3 協議会 第2回（骨子案・見込量・保険料・成果指標）
+9-4 協議会 第3回（素案）
+9-5 パブリックコメントの様式作成
+9-6 パブリックコメントの実施
+9-7 意見への対応
+9-8 協議会 第4回（最終案）</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>成果品①</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>3-1 給付費等分析結果報告書の作成
+3-3 成果品①の製本・納品</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>成果品②</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>7-7 サービス見込量推計結果報告書の作成
+7-8 成果品②の製本・納品</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>成果品③</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>6-1 骨子案の作成
+6-3 成果品③の製本・納品</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>成果品④</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>8-1 素案の作成
+8-6 成果品④の製本・納品</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>成果品⑤</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>10-2 レイアウト・組版
+10-3 校正（初校・再校・校了）
+10-6 印刷・製本</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>成果品⑥</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>10-4 概要版の構成案
+10-5 概要版の作成
+10-6 印刷・製本</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>成果品</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>10-7 データCD-Rの作成</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>5(1)</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>本業務の実施に必要な資料等は、小野町が受託者に貸与するものとする。</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>1-6 町への資料依頼票の作成
+1-7 町データの受領</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>5(2)</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>受託者は、本業務実施中及び終了後に関わらず、業務上知り得た一切の個人情報については、個人情報の保護に関する法律及び小野町個人情報保護条例等を遵守し、情報の保護に努め、適正に個人情報の取り扱いを行うこと。</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>前提条項</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>5(3)</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>本仕様書に定めのない事項及び疑義が生じた場合は、小野町と受託者で協議するものとする。</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>1-8 工程・協議会日程の合意と確認事項の照会</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>公告10⑥</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>研究員は「見える化」システムやニーズ調査など各種データから介護給付費の統計分析により将来のサービス量を推計し計画化できる者（公告第1-19号 10⑥）</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>1-1 契約・体制の確立、キックオフ</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>※ 「要確認」は、01_WBS に対応する作業が置かれていない条項です。業務の抜けを疑ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>※ 「前提条項」は、目的・計画期間・個人情報の取扱いなど、作業として分解せず業務全体で担保する条項です。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="64" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1429,45 +2382,50 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>仕様書根拠</t>
+          <t>仕様書 条項</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
+          <t>仕様書の記載内容（原文）</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>予定開始</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>予定完了</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>進捗率</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>重み</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>実績・根拠</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>前提条件・ブロッカー</t>
         </is>
@@ -1494,43 +2452,48 @@
           <t>実施体制、役割分担、連絡系統</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>公告10⑥（技術者の配置）</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>【公告10⑥】研究員は「見える化」システムやニーズ調査など各種データから介護給付費の統計分析により将来のサービス量を推計し計画化できる者（公告第1-19号 10⑥）</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J2" s="18" t="n">
+      <c r="K2" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K2" s="19" t="n">
+      <c r="L2" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>キックオフ資料・業務計画書（02_キックオフ・業務計画）</t>
         </is>
       </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1557,43 +2520,48 @@
           <t>前受託者からの引継ぎ資料の棚卸しと索引化</t>
         </is>
       </c>
-      <c r="E3" s="15" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="K3" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K3" s="19" t="n">
+      <c r="L3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="15" t="inlineStr">
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>manifest_全ファイル（207ファイル）</t>
         </is>
       </c>
-      <c r="M3" s="15" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1620,43 +2588,48 @@
           <t>原典4件（公告・仕様書×2計画）を読み、成果品要件・工程・作業分担を確定</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>仕様書全般</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="K4" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="L4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="15" t="inlineStr">
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>仕様書適合性チェック 第2版（00_引継ぎ）。初版8/3、第2版8/13</t>
         </is>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1683,43 +2656,48 @@
           <t>5章構成・基本理念・3基本目標・14施策、標準給付費3,566,486千円、保険料6,600円の算定根拠</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)】基礎的な地域データ及び資料の整理分析（現状分析）。高齢者福祉・介護保険をめぐる施策の動向、小野町の概要及び社会経済的特性、地域福祉資源の整備状況、高齢者の現況動向及びサービスの利用状況等について、小野町が提供するデータをもとに整理分析を行う。（計画策定の検討資料として活用するため、各種事項の将来推計を行う。なお、推計にあたっては、可能な限り細分化する）</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="K5" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="L5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="15" t="inlineStr">
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>第9期計画本文（13_関連計画）。骨子案第3版・成果品①第5版に反映</t>
         </is>
       </c>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1746,43 +2724,48 @@
           <t>重複5施策を特定。成年後見は移管、虐待防止・災害対応・支え合いは連携</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>仕様書2(2)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>【2(2)】国が示す第10期計画に関する基本的な考え方を踏まえた上で、本町の特性を活かした計画とする。</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="K6" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K6" s="19" t="n">
+      <c r="L6" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="M6" s="15" t="inlineStr">
         <is>
           <t>地域福祉計画との整合確認メモ（03_計画素案）</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1809,43 +2792,48 @@
           <t>依頼35項目＋確認事項12件。基準日・年度範囲・単位・様式まで指定</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>仕様書5(1)（資料は町が貸与）</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>【5(1)】本業務の実施に必要な資料等は、小野町が受託者に貸与するものとする。</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="K7" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K7" s="19" t="n">
+      <c r="L7" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L7" s="15" t="inlineStr">
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <t>小野町_データ依頼票（16_町データ依頼）</t>
         </is>
       </c>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1872,43 +2860,48 @@
           <t>依頼票に基づく資料・データの受領</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>【5(1)】本業務の実施に必要な資料等は、小野町が受託者に貸与するものとする。</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="K8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="19" t="n">
+      <c r="L8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L8" s="15" t="inlineStr">
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t>受領0件／依頼35件</t>
         </is>
       </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="N8" s="15" t="inlineStr">
         <is>
           <t>**町の回答。P5・P7・P8のほぼ全てがこれに依存する**</t>
         </is>
@@ -1917,63 +2910,68 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>P2 統計分析</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-8</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>人口・世帯の分析</t>
+          <t>工程・協議会日程の合意と確認事項の照会</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>総人口、高齢化率、前期・後期高齢者、世帯。令和32年まで推計</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①ア</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>高齢者計画の仕様書には工程表がないため、業務期間から逆算した工程と協議会の回数・時期を町と合意する。あわせて仕様書の疑義4件を照会する</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>仕様書5(3)</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>【5(3)】本仕様書に定めのない事項及び疑義が生じた場合は、小野町と受託者で協議するものとする。</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H9" s="16" t="inlineStr">
         <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>基礎数値整理ブック（A系13ファイル）</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="L9" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**工程変更協議資料と確認事項12件を作成済み（うち高齢者に係るもの8件）**</t>
+        </is>
+      </c>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>**町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない**</t>
         </is>
       </c>
     </row>
@@ -1985,56 +2983,61 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>第1号被保険者の分析</t>
+          <t>人口・世帯の分析</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>被保険者数の推移と推計</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="inlineStr">
+          <t>総人口、高齢化率、前期・後期高齢者、世帯。令和32年まで推計</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①ア</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①ア】統計分析（ア）人口</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="K10" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K10" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>B系4ファイル</t>
-        </is>
+      <c r="L10" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>基礎数値整理ブック（A系13ファイル）</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2048,56 +3051,61 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>認定者数・認定率の分析</t>
+          <t>第1号被保険者の分析</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>平成19年3月末〜令和8年3月末の20期。要介護度別7区分・年齢階層別・被保険者区分別</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①イ</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+          <t>被保険者数の推移と推計</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①ア</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①ア】統計分析（ア）人口</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H11" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="K11" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K11" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>要支援要介護認定者数の整理（07_見える化整理・10シート）。第1号＋第2号＝全体を20期で検算済み</t>
-        </is>
+      <c r="L11" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>B系4ファイル</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2111,58 +3119,63 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>認定者数の異常値の検証</t>
+          <t>認定者数・認定率の分析</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>令和8年3月末の▲152人（▲16.1％）の要因分析。県内59市町村との比較</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
+          <t>平成19年3月末〜令和8年3月末の20期。要介護度別7区分・年齢階層別・被保険者区分別</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①イ</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①イ】統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>**減少の77.0％が85歳以上に集中。県内で唯一4.3σの外れ値。**3出典を基準日順に配列し、令和7年7月まで一貫増加を確認</t>
-        </is>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>**町の認定台帳による確認（依頼票N1〜N4）。本業務の最大の律速**</t>
+          <t>要支援要介護認定者数の整理（07_見える化整理・10シート）。第1号＋第2号＝全体を20期で検算済み</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2174,32 +3187,32 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>サービス受給者数の分析</t>
+          <t>認定者数の異常値の検証</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>居宅・施設・地域密着型の受給者数</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①ウ</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>令和8年3月末の▲152人（▲16.1％）の要因分析。県内59市町村との比較</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①イ</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①イ】統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H13" s="16" t="inlineStr">
@@ -2207,25 +3220,30 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>地域分析ブック（D1〜D4、D32系）</t>
-        </is>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="M13" s="15" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**減少の77.0％が85歳以上に集中。県内で唯一4.3σの外れ値。**3出典を基準日順に配列し、令和7年7月まで一貫増加を確認</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>**町の認定台帳による確認（依頼票N1〜N4）。本業務の最大の律速**</t>
         </is>
       </c>
     </row>
@@ -2237,58 +3255,63 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>介護予防事業対象者数の分析</t>
+          <t>サービス受給者数の分析</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>総合事業対象者、通いの場参加者</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①エ</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+          <t>居宅・施設・地域密着型の受給者数</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①ウ</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①ウ】統計分析（ウ）居宅サービス・施設サービス・地域密着型サービスの受給者数</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="K14" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>**見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録</t>
-        </is>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>**町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない**</t>
+          <t>地域分析ブック（D1〜D4、D32系）</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2300,58 +3323,63 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>認知症高齢者の分析</t>
+          <t>介護予防事業対象者数の分析</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>認知症高齢者の日常生活自立度、認知症施策の実施状況</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①イ・2(3)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
+          <t>総合事業対象者、通いの場参加者</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①エ</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①エ】統計分析（エ）介護予防事業対象者数</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>J16〜J18を取得。自立度Ⅱa 68→148人、M 7→29人</t>
-        </is>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）</t>
+          <t>**見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="inlineStr">
+        <is>
+          <t>**町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない**</t>
         </is>
       </c>
     </row>
@@ -2363,58 +3391,64 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>サービス自給率の分析</t>
+          <t>認知症高齢者の分析</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>県内59市町村との比較。自給率67.57％</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①オ</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+          <t>認知症高齢者の日常生活自立度、認知症施策の実施状況</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①イ・2(3)</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①イ】統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数
+【2(3)】国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K16" s="19" t="n">
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>δ2・δ3系12指標</t>
-        </is>
-      </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>J16〜J18を取得。自立度Ⅱa 68→148人、M 7→29人</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）</t>
         </is>
       </c>
     </row>
@@ -2426,58 +3460,63 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>介護保険財政の分析</t>
+          <t>サービス自給率の分析</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>歳入歳出、基金、繰越金</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(2)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
+          <t>県内59市町村との比較。自給率67.57％</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①オ</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①オ】統計分析（オ）その他計画策定に必要な推計</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" s="15" t="inlineStr">
-        <is>
-          <t>財政整理ブック（D47・D48系25指標、H26〜R5）。繰越金182.0百万円・基金純増88.1百万円</t>
-        </is>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>令和6・7年度の決算（依頼票S7）。年報ベースのためR6・R7が未反映</t>
+          <t>δ2・δ3系12指標</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -2489,121 +3528,131 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>見える化 優先度C分野の出力</t>
+          <t>介護保険財政の分析</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携、医療提供体制、リハビリ提供体制、保険者機能強化推進交付金の評価指標</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)①オ</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+          <t>歳入歳出、基金、繰越金</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(2)</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="L18" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>見える化システムへのアクセス</t>
+          <t>財政整理ブック（D47・D48系25指標、H26〜R5）。繰越金182.0百万円・基金純増88.1百万円</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>令和6・7年度の決算（依頼票S7）。年報ベースのためR6・R7が未反映</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>P3 給付費等の分析</t>
+          <t>P2 統計分析</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>給付費等分析結果報告書の作成</t>
+          <t>見える化 優先度C分野の出力</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>サービス費目ごとの給付費・地域支援事業の分析、制度改正の影響</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)②・成果品①</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+          <t>在宅医療・介護連携、医療提供体制、リハビリ提供体制、保険者機能強化推進交付金の評価指標</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)①オ</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)①オ】統計分析（オ）その他計画策定に必要な推計</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J19" s="18" t="n">
-        <v>70</v>
-      </c>
-      <c r="K19" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" s="15" t="inlineStr">
-        <is>
-          <t>**第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
-        </is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t>見える化システムへのアクセス</t>
         </is>
       </c>
     </row>
@@ -2615,58 +3664,64 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>町の給付実績との突合</t>
+          <t>給付費等分析結果報告書の作成</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>見える化システムの値と町の給付実績の突合</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)②</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
+          <t>サービス費目ごとの給付費・地域支援事業の分析、制度改正の影響</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)②・成果品①</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
+【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>70</v>
+      </c>
+      <c r="L20" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>町の給付実績（依頼票S1・S2）</t>
+          <t>**第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
       </c>
     </row>
@@ -2678,121 +3733,131 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>成果品①の製本・納品</t>
+          <t>町の給付実績との突合</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品①</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+          <t>見える化システムの値と町の給付実績の突合</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)②</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="K21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="15" t="inlineStr">
+      <c r="L21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M21" s="15" t="inlineStr">
-        <is>
-          <t>報告書の確定</t>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>町の給付実績（依頼票S1・S2）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>P4 調査結果の反映</t>
+          <t>P3 給付費等の分析</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>調査結果報告書の確認</t>
+          <t>成果品①の製本・納品</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>令和8年3月・104頁の報告書の内容確認と妥当性の検証</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)③</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品①</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L22" s="15" t="inlineStr">
-        <is>
-          <t>単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。報告書内の不整合3件を指摘</t>
-        </is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
           <t>―</t>
+        </is>
+      </c>
+      <c r="N22" s="15" t="inlineStr">
+        <is>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
@@ -2804,56 +3869,61 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>集計データの整理</t>
+          <t>調査結果報告書の確認</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>リスク10項目×9区分の保持</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
+          <t>令和8年3月・104頁の報告書の内容確認と妥当性の検証</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I23" s="17" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="K23" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K23" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" s="15" t="inlineStr">
-        <is>
-          <t>集計データ整理ブック（14_アンケート集計・9シート）</t>
-        </is>
+      <c r="L23" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M23" s="15" t="inlineStr">
+        <is>
+          <t>単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。報告書内の不整合3件を指摘</t>
+        </is>
+      </c>
+      <c r="N23" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2867,56 +3937,61 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>集計結果・分析報告書の作成</t>
+          <t>集計データの整理</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>単純集計、リスク分析、前回対比、8つの分析、第9期課題への到達状況、第10期への示唆</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="inlineStr">
+          <t>リスク10項目×9区分の保持</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I24" s="17" t="inlineStr">
+      <c r="J24" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="K24" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K24" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>**7章・72表・約27,800字（14_アンケート集計）**</t>
-        </is>
+      <c r="L24" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M24" s="15" t="inlineStr">
+        <is>
+          <t>集計データ整理ブック（14_アンケート集計・9シート）</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2930,56 +4005,61 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>クロス集計の設計</t>
+          <t>集計結果・分析報告書の作成</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>前回計画の課題に基づくクロス集計25件の設計</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
+          <t>単純集計、リスク分析、前回対比、8つの分析、第9期課題への到達状況、第10期への示唆</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="J25" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="K25" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K25" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>クロス集計設計書（8シート・25件）。4件掲載済、17件が個票を要し、4件は設問なし</t>
-        </is>
+      <c r="L25" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M25" s="15" t="inlineStr">
+        <is>
+          <t>**7章・72表・約27,800字（14_アンケート集計）**</t>
+        </is>
+      </c>
+      <c r="N25" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2993,58 +4073,63 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>個票によるクロス集計</t>
+          <t>クロス集計の設計</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>要介護度別・世帯構成別のクロス集計17件</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
+          <t>前回計画の課題に基づくクロス集計25件の設計</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L26" s="15" t="inlineStr">
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L26" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" s="15" t="inlineStr">
+        <is>
+          <t>クロス集計設計書（8シート・25件）。4件掲載済、17件が個票を要し、4件は設問なし</t>
+        </is>
+      </c>
+      <c r="N26" s="15" t="inlineStr">
         <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="M26" s="15" t="inlineStr">
-        <is>
-          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
     </row>
@@ -3056,119 +4141,129 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>レッドチームレビュー</t>
+          <t>個票によるクロス集計</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>集計・分析の反証検証</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
+          <t>要介護度別・世帯構成別のクロス集計17件</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)③</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="K27" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J27" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="15" t="inlineStr">
-        <is>
-          <t>REDTEAM 2本（14_アンケート集計）。数値の取り違え1件を自己検出し修正</t>
-        </is>
-      </c>
-      <c r="M27" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="N27" s="15" t="inlineStr">
+        <is>
+          <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>P5 第9期の評価</t>
+          <t>P4 調査結果の反映</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>協議会資料（第9期評価・調査結果）の作成</t>
+          <t>レッドチームレビュー</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>第9期が第5章2(2)で自ら定める4点検項目に沿って評価</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)②・4(5)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
+          <t>集計・分析の反証検証</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="I28" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J28" s="18" t="n">
+      <c r="K28" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K28" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" s="15" t="inlineStr">
-        <is>
-          <t>**協議会資料（08_協議会資料・42表・約23,500字）**</t>
-        </is>
+      <c r="L28" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>REDTEAM 2本（14_アンケート集計）。数値の取り違え1件を自己検出し修正</t>
+        </is>
+      </c>
+      <c r="N28" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3182,58 +4277,64 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>成果目標の達成状況の確定</t>
+          <t>協議会資料（第9期評価・調査結果）の作成</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>第9期の見込みと実績の対比</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(1)②</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
+          <t>第9期が第5章2(2)で自ら定める4点検項目に沿って評価</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)②・4(5)</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
+【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
-        </is>
-      </c>
-      <c r="J29" s="18" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>見込みと実績の対比の枠は作成済み（成果品①第7章7、骨子案 参考1）</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K29" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M29" s="15" t="inlineStr">
         <is>
-          <t>町の事業実績・給付実績（依頼票H1〜H15）</t>
+          <t>**協議会資料（08_協議会資料・42表・約23,500字）**</t>
+        </is>
+      </c>
+      <c r="N29" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3245,121 +4346,131 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>施設整備方針との不整合の確認</t>
+          <t>成果目標の達成状況の確定</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>第9期は新規整備を行わない方針だが、認知症対応型共同生活介護の定員が27人（38.0％）増</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
+          <t>第9期の見込みと実績の対比</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)②</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="L30" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>整備の経緯の確認（依頼票H15）</t>
+          <t>見込みと実績の対比の枠は作成済み（成果品①第7章7、骨子案 参考1）</t>
+        </is>
+      </c>
+      <c r="N30" s="15" t="inlineStr">
+        <is>
+          <t>町の事業実績・給付実績（依頼票H1〜H15）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>P6 骨子案</t>
+          <t>P5 第9期の評価</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>施設整備方針との不整合の確認</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>基本課題・施策方向・重点課題・施策体系</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(3)・成果品③</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>第9期は新規整備を行わない方針だが、認知症対応型共同生活介護の定員が27人（38.0％）増</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)②</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J31" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="K31" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" s="15" t="inlineStr">
-        <is>
-          <t>**第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
-        </is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K31" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
-          <t>実績データによる数値の確定</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N31" s="15" t="inlineStr">
+        <is>
+          <t>整備の経緯の確認（依頼票H15）</t>
         </is>
       </c>
     </row>
@@ -3371,58 +4482,64 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>骨子案の協議（協議会）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>基本理念・基本目標・施策体系の合意</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(3)・4(5)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+          <t>基本課題・施策方向・重点課題・施策体系</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(3)・成果品③</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I32" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J32" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K32" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
+          <t>**第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
+        </is>
+      </c>
+      <c r="N32" s="15" t="inlineStr">
+        <is>
+          <t>実績データによる数値の確定</t>
         </is>
       </c>
     </row>
@@ -3434,121 +4551,132 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>成果品③の製本・納品</t>
+          <t>骨子案の協議（協議会）</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品③</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>基本理念・基本目標・施策体系の合意</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(3)・4(5)</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I33" s="20" t="inlineStr">
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J33" s="18" t="n">
+      <c r="K33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="15" t="inlineStr">
+      <c r="L33" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M33" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M33" s="15" t="inlineStr">
-        <is>
-          <t>骨子案の確定</t>
+      <c r="N33" s="15" t="inlineStr">
+        <is>
+          <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>P7 推計・算定</t>
+          <t>P6 骨子案</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>算定シートの構築</t>
+          <t>成果品③の製本・納品</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>サービス54区分の単価×量から給付費、標準給付費、保険料までを算式でつなぐ</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(2)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品③</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J34" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K34" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" s="15" t="inlineStr">
-        <is>
-          <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,442円 対 実際6,600円。差2.4％は仮置き値による）</t>
-        </is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J34" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K34" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
           <t>―</t>
+        </is>
+      </c>
+      <c r="N34" s="15" t="inlineStr">
+        <is>
+          <t>骨子案の確定</t>
         </is>
       </c>
     </row>
@@ -3560,56 +4688,61 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>保険料算定のケース設定の確定</t>
+          <t>算定シートの構築</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>標準（低位・高位）、施設整備あり、制度改正の影響、基金活用、保険料据置の逆算</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
+          <t>サービス54区分の単価×量から給付費、標準給付費、保険料までを算式でつなぐ</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J35" s="18" t="n">
+      <c r="K35" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K35" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="15" t="inlineStr">
-        <is>
-          <t>**C1〜C6。引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する施設整備・制度改正に対応していなかった**</t>
-        </is>
+      <c r="L35" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M35" s="15" t="inlineStr">
+        <is>
+          <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,442円 対 実際6,600円。差2.4％は仮置き値による）</t>
+        </is>
+      </c>
+      <c r="N35" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3623,58 +4756,63 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>被保険者数・認定者数の推計</t>
+          <t>保険料算定のケース設定の確定</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>人口推計に年齢階層別の認定率を乗じる自然体推計</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
+          <t>標準（低位・高位）、施設整備あり、制度改正の影響、基金活用、保険料据置の逆算</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I36" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>算式は実装済み（03_認定者推計）</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J36" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K36" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>**認定者数の確定（2-4）**</t>
+          <t>**C1〜C6。引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する施設整備・制度改正に対応していなかった**</t>
+        </is>
+      </c>
+      <c r="N36" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -3686,58 +4824,63 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>サービス見込量の推計</t>
+          <t>被保険者数・認定者数の推計</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>サービス種類別の利用者数・量・給付費</t>
-        </is>
-      </c>
-      <c r="E37" s="15" t="inlineStr">
+          <t>人口推計に年齢階層別の認定率を乗じる自然体推計</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I37" s="20" t="inlineStr">
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J37" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J37" s="18" t="n">
+      <c r="K37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" s="15" t="inlineStr">
-        <is>
-          <t>算式は実装済み（05・06_見込量）</t>
-        </is>
+      <c r="L37" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M37" s="15" t="inlineStr">
         <is>
-          <t>**認定者数の確定（2-4）、町の給付実績（依頼票S1・S2）**</t>
+          <t>算式は実装済み（03_認定者推計）</t>
+        </is>
+      </c>
+      <c r="N37" s="15" t="inlineStr">
+        <is>
+          <t>**認定者数の確定（2-4）**</t>
         </is>
       </c>
     </row>
@@ -3749,58 +4892,63 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>7-5</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>見える化システムへの入力作業</t>
+          <t>サービス見込量の推計</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>出力の分析だけでなく、システムへの入力が業務に含まれる</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
+          <t>サービス種類別の利用者数・量・給付費</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J38" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J38" s="18" t="n">
+      <c r="K38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L38" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）**</t>
+          <t>算式は実装済み（05・06_見込量）</t>
+        </is>
+      </c>
+      <c r="N38" s="15" t="inlineStr">
+        <is>
+          <t>**認定者数の確定（2-4）、町の給付実績（依頼票S1・S2）**</t>
         </is>
       </c>
     </row>
@@ -3812,58 +4960,63 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>7-6</t>
+          <t>7-5</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>保険料のケース別算定</t>
+          <t>見える化システムへの入力作業</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>ケースC1〜C6ごとの保険料基準額の算定</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
+          <t>出力の分析だけでなく、システムへの入力が業務に含まれる</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J39" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J39" s="18" t="n">
+      <c r="K39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" s="15" t="inlineStr">
-        <is>
-          <t>算式は実装済み（09_保険料算定）</t>
-        </is>
+      <c r="L39" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>見込量の確定、基金残高・所得段階別人数・収納率（依頼票S3〜S5）</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N39" s="15" t="inlineStr">
+        <is>
+          <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）**</t>
         </is>
       </c>
     </row>
@@ -3875,58 +5028,63 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>7-7</t>
+          <t>7-6</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>サービス見込量推計結果報告書の作成</t>
+          <t>保険料のケース別算定</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>成果品②の本体</t>
-        </is>
-      </c>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品②</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="inlineStr">
+          <t>ケースC1〜C6ごとの保険料基準額の算定</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(2)</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
+        <is>
+          <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I40" s="20" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J40" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J40" s="18" t="n">
+      <c r="K40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="19" t="n">
+      <c r="L40" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>算定シートが素材。章立ては未作成</t>
-        </is>
-      </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>見込量・保険料の算定</t>
+          <t>算式は実装済み（09_保険料算定）</t>
+        </is>
+      </c>
+      <c r="N40" s="15" t="inlineStr">
+        <is>
+          <t>見込量の確定、基金残高・所得段階別人数・収納率（依頼票S3〜S5）</t>
         </is>
       </c>
     </row>
@@ -3938,121 +5096,131 @@
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>7-7</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>成果品②の製本・納品</t>
+          <t>サービス見込量推計結果報告書の作成</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
+          <t>成果品②の本体</t>
+        </is>
+      </c>
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品②</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>【成果品②】（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I41" s="20" t="inlineStr">
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J41" s="18" t="n">
+      <c r="K41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L41" s="19" t="n">
+        <v>4</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
-          <t>報告書の確定</t>
+          <t>算定シートが素材。章立ては未作成</t>
+        </is>
+      </c>
+      <c r="N41" s="15" t="inlineStr">
+        <is>
+          <t>見込量・保険料の算定</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>P8 素案</t>
+          <t>P7 推計・算定</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>成果品②の製本・納品</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>骨子案を踏まえた計画素案。12施策の本文</t>
-        </is>
-      </c>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(3)・成果品④</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr">
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品②</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>【成果品②】（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I42" s="19" t="inlineStr">
-        <is>
-          <t>進行中</t>
-        </is>
-      </c>
-      <c r="J42" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="K42" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="L42" s="15" t="inlineStr">
-        <is>
-          <t>**第2版（5章＋資料編・67表・約32,000字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。未確定156箇所を5区分で明示</t>
-        </is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K42" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>見込量・保険料（P7）、成果指標の現状値（依頼票H1〜H15）</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N42" s="15" t="inlineStr">
+        <is>
+          <t>報告書の確定</t>
         </is>
       </c>
     </row>
@@ -4064,58 +5232,64 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
-          <t>成果指標の目標値案の作成</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>40指標の目標値案と根拠の型</t>
-        </is>
-      </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(3)</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="inlineStr">
+          <t>骨子案を踏まえた計画素案。12施策の本文</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(3)・成果品④</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J43" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K43" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="15" t="inlineStr">
-        <is>
-          <t>**成果指標目標値案（03_計画素案・40指標）。**現状値が未受領の20指標は算定規則として案を置いた</t>
-        </is>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="K43" s="18" t="n">
+        <v>65</v>
+      </c>
+      <c r="L43" s="19" t="n">
+        <v>5</v>
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**第2版（5章＋資料編・67表・約32,000字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。未確定156箇所を5区分で明示</t>
+        </is>
+      </c>
+      <c r="N43" s="15" t="inlineStr">
+        <is>
+          <t>見込量・保険料（P7）、成果指標の現状値（依頼票H1〜H15）</t>
         </is>
       </c>
     </row>
@@ -4127,58 +5301,63 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>認知症施策推進基本計画の包含方針</t>
+          <t>成果指標の目標値案の作成</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>基本的施策12項目との対応表、包含の形式</t>
-        </is>
-      </c>
-      <c r="E44" s="15" t="inlineStr">
-        <is>
-          <t>仕様書2(3)</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
+          <t>40指標の目標値案と根拠の型</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(3)</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H44" s="16" t="inlineStr">
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="J44" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="K44" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="K44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="15" t="inlineStr">
-        <is>
-          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案</t>
-        </is>
+      <c r="L44" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>町の意思決定（方式A／B）</t>
+          <t>**成果指標目標値案（03_計画素案・40指標）。**現状値が未受領の20指標は算定規則として案を置いた</t>
+        </is>
+      </c>
+      <c r="N44" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -4190,58 +5369,63 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
-          <t>見込量・保険料・成果指標の反映</t>
+          <t>認知症施策推進基本計画の包含方針</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>素案の未確定156箇所の解消</t>
-        </is>
-      </c>
-      <c r="E45" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(3)</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
+          <t>基本的施策12項目との対応表、包含の形式</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>仕様書2(3)</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>【2(3)】国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
       <c r="H45" s="16" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J45" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L45" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J45" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K45" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M45" s="15" t="inlineStr">
         <is>
-          <t>**P7の完了、町データの受領**</t>
+          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案</t>
+        </is>
+      </c>
+      <c r="N45" s="15" t="inlineStr">
+        <is>
+          <t>町の意思決定（方式A／B）</t>
         </is>
       </c>
     </row>
@@ -4253,58 +5437,63 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>8-5</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>素案の協議（協議会）</t>
+          <t>見込量・保険料・成果指標の反映</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>素案の内容の合意</t>
-        </is>
-      </c>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(3)・4(5)</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+          <t>素案の未確定156箇所の解消</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(3)</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J46" s="18" t="n">
+      <c r="K46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K46" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="L46" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M46" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M46" s="15" t="inlineStr">
-        <is>
-          <t>協議会の開催時期</t>
+      <c r="N46" s="15" t="inlineStr">
+        <is>
+          <t>**P7の完了、町データの受領**</t>
         </is>
       </c>
     </row>
@@ -4316,121 +5505,132 @@
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>8-6</t>
+          <t>8-5</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>成果品④の製本・納品</t>
+          <t>素案の協議（協議会）</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>データCD-R1部＋冊子（簡易製本）3部</t>
-        </is>
-      </c>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品④</t>
-        </is>
-      </c>
-      <c r="F47" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>素案の内容の合意</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(3)・4(5)</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
+【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H47" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I47" s="20" t="inlineStr">
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="K47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="15" t="inlineStr">
+      <c r="L47" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M47" s="15" t="inlineStr">
-        <is>
-          <t>素案の確定</t>
+      <c r="N47" s="15" t="inlineStr">
+        <is>
+          <t>協議会の開催時期</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>P9 意見聴取</t>
+          <t>P8 素案</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-6</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>協議会の開催回数・時期の確定</t>
+          <t>成果品④の製本・納品</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>小野町高齢者福祉サービス推進協議会</t>
-        </is>
-      </c>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(5)</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="inlineStr">
-        <is>
-          <t>町</t>
+          <t>データCD-R1部＋冊子（簡易製本）3部</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品④</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I48" s="22" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="n">
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J48" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="19" t="n">
+      <c r="L48" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="15" t="inlineStr">
-        <is>
-          <t>**仕様書に回数の指定がない。**受託者案は4回</t>
-        </is>
-      </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N48" s="15" t="inlineStr">
+        <is>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -4442,58 +5642,63 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-1</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>協議会 第1回（第9期の評価・調査結果）</t>
+          <t>協議会の開催回数・時期の確定</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>評価と調査結果の報告</t>
-        </is>
-      </c>
-      <c r="E49" s="15" t="inlineStr">
+          <t>小野町高齢者福祉サービス推進協議会</t>
+        </is>
+      </c>
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F49" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="I49" s="22" t="inlineStr">
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="J49" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="K49" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="15" t="inlineStr">
-        <is>
-          <t>**資料は作成済み（08_協議会資料・42表）**</t>
-        </is>
+      <c r="K49" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M49" s="15" t="inlineStr">
         <is>
-          <t>**開催日が未定**</t>
+          <t>**仕様書に回数の指定がない。**受託者案は4回</t>
+        </is>
+      </c>
+      <c r="N49" s="15" t="inlineStr">
+        <is>
+          <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
         </is>
       </c>
     </row>
@@ -4505,58 +5710,63 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
+          <t>協議会 第1回（第9期の評価・調査結果）</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>計画の骨格の合意</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
+          <t>評価と調査結果の報告</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
       <c r="H50" s="16" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="I50" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J50" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="19" t="n">
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J50" s="21" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="L50" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>骨子案第3版・成果指標目標値案は作成済み</t>
-        </is>
-      </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>P7の完了、開催日の確定</t>
+          <t>**資料は作成済み（08_協議会資料・42表）**</t>
+        </is>
+      </c>
+      <c r="N50" s="15" t="inlineStr">
+        <is>
+          <t>**開催日が未定**</t>
         </is>
       </c>
     </row>
@@ -4568,58 +5778,63 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>協議会 第3回（素案）</t>
+          <t>協議会 第2回（骨子案・見込量・保険料・成果指標）</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>素案の合意</t>
-        </is>
-      </c>
-      <c r="E51" s="15" t="inlineStr">
+          <t>計画の骨格の合意</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
       <c r="H51" s="16" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="I51" s="20" t="inlineStr">
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="K51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="19" t="n">
+      <c r="L51" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L51" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
       <c r="M51" s="15" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>骨子案第3版・成果指標目標値案は作成済み</t>
+        </is>
+      </c>
+      <c r="N51" s="15" t="inlineStr">
+        <is>
+          <t>P7の完了、開催日の確定</t>
         </is>
       </c>
     </row>
@@ -4631,58 +5846,63 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>協議会 第3回（素案）</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>実施要領、意見提出様式、意見と町の考え方の対応表</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
+          <t>素案の合意</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J52" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K52" s="19" t="n">
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L52" s="15" t="inlineStr">
-        <is>
-          <t>計画策定業務設計書 第4章（02_キックオフ・業務計画）</t>
-        </is>
-      </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
           <t>―</t>
+        </is>
+      </c>
+      <c r="N52" s="15" t="inlineStr">
+        <is>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -4694,58 +5914,63 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>意見提出期間1か月</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
+          <t>実施要領、意見提出様式、意見と町の考え方の対応表</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>町</t>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="H53" s="16" t="inlineStr">
         <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="I53" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J53" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="19" t="n">
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K53" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L53" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L53" s="15" t="inlineStr">
+      <c r="M53" s="15" t="inlineStr">
+        <is>
+          <t>計画策定業務設計書 第4章（02_キックオフ・業務計画）</t>
+        </is>
+      </c>
+      <c r="N53" s="15" t="inlineStr">
         <is>
           <t>―</t>
-        </is>
-      </c>
-      <c r="M53" s="15" t="inlineStr">
-        <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4757,58 +5982,63 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>意見の整理、対応案の作成、計画への反映</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
+          <t>意見提出期間1か月</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>町</t>
         </is>
       </c>
       <c r="H54" s="16" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="I54" s="20" t="inlineStr">
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="J54" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J54" s="18" t="n">
+      <c r="K54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="19" t="n">
+      <c r="L54" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L54" s="15" t="inlineStr">
-        <is>
-          <t>対応表の様式は作成済み</t>
-        </is>
-      </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N54" s="15" t="inlineStr">
+        <is>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -4820,119 +6050,129 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>9-8</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>協議会 第4回（最終案）</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>最終案の確認</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
+          <t>意見の整理、対応案の作成、計画への反映</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="H55" s="16" t="inlineStr">
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I55" s="20" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J55" s="18" t="n">
+      <c r="K55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K55" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L55" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M55" s="15" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>対応表の様式は作成済み</t>
+        </is>
+      </c>
+      <c r="N55" s="15" t="inlineStr">
+        <is>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>P10 完成・納品</t>
+          <t>P9 意見聴取</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>9-8</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>計画書の原稿確定</t>
+          <t>協議会 第4回（最終案）</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>パブリックコメント対応後の原稿</t>
-        </is>
-      </c>
-      <c r="E56" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4(4)</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>最終案の確認</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(5)</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
+          <t>受託者・町</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="H56" s="16" t="inlineStr">
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I56" s="20" t="inlineStr">
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J56" s="18" t="n">
+      <c r="K56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" s="15" t="inlineStr">
+      <c r="L56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr">
         <is>
           <t>意見への対応</t>
         </is>
@@ -4946,58 +6186,63 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
-          <t>レイアウト・組版</t>
+          <t>計画書の原稿確定</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>A4・4色刷り・80頁程度</t>
-        </is>
-      </c>
-      <c r="E57" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品⑤</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
+          <t>パブリックコメント対応後の原稿</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(4)</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="inlineStr">
+        <is>
+          <t>【4(4)】最終調整及び計画書の作成・取りまとめ。（1）から（3）の結果を踏まえ、小野町高齢者保健福祉計画・第10期介護保険事業計画書を作成するものとする。</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G57" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="H57" s="16" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I57" s="20" t="inlineStr">
+      <c r="J57" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J57" s="18" t="n">
+      <c r="K57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K57" s="19" t="n">
+      <c r="L57" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L57" s="15" t="inlineStr">
+      <c r="M57" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M57" s="15" t="inlineStr">
-        <is>
-          <t>原稿の確定</t>
+      <c r="N57" s="15" t="inlineStr">
+        <is>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -5009,58 +6254,63 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>10-3</t>
+          <t>10-2</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>校正（初校・再校・校了）</t>
+          <t>レイアウト・組版</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>町の確認を経て校了</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
+          <t>A4・4色刷り・80頁程度</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑤</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>受託者・町</t>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="H58" s="16" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I58" s="20" t="inlineStr">
+      <c r="J58" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J58" s="18" t="n">
+      <c r="K58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K58" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L58" s="15" t="inlineStr">
-        <is>
-          <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）**</t>
-        </is>
+      <c r="L58" s="19" t="n">
+        <v>3</v>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>組版</t>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N58" s="15" t="inlineStr">
+        <is>
+          <t>原稿の確定</t>
         </is>
       </c>
     </row>
@@ -5072,58 +6322,63 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>10-4</t>
+          <t>10-3</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>概要版の構成案</t>
+          <t>校正（初校・再校・校了）</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>A4・4色刷り・8頁のページ割り</t>
-        </is>
-      </c>
-      <c r="E59" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品⑥</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>受託者</t>
+          <t>町の確認を経て校了</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品⑤</t>
+        </is>
+      </c>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="H59" s="16" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-      <c r="J59" s="18" t="n">
-        <v>100</v>
-      </c>
-      <c r="K59" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="15" t="inlineStr">
-        <is>
-          <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）</t>
-        </is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J59" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M59" s="15" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）**</t>
+        </is>
+      </c>
+      <c r="N59" s="15" t="inlineStr">
+        <is>
+          <t>組版</t>
         </is>
       </c>
     </row>
@@ -5135,58 +6390,63 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>10-5</t>
+          <t>10-4</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>概要版の作成</t>
+          <t>概要版の構成案</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>計画書からの抽出とリライト、図表8点程度</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
+          <t>A4・4色刷り・8頁のページ割り</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑥</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
       <c r="H60" s="16" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I60" s="20" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="J60" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>構成案は作成済み</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J60" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="K60" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>計画書の確定</t>
+          <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）</t>
+        </is>
+      </c>
+      <c r="N60" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -5198,58 +6458,63 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>10-6</t>
+          <t>10-5</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>印刷・製本</t>
+          <t>概要版の作成</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>計画書50部、概要版50部。色校正を含む</t>
-        </is>
-      </c>
-      <c r="E61" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品⑤⑥</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
+          <t>計画書からの抽出とリライト、図表8点程度</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品⑥</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="H61" s="16" t="inlineStr">
-        <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="I61" s="20" t="inlineStr">
+      <c r="J61" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J61" s="18" t="n">
+      <c r="K61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="19" t="n">
+      <c r="L61" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="L61" s="15" t="inlineStr">
-        <is>
-          <t>**逆算表を作成済み。12月までに印刷業者を押さえる必要がある**</t>
-        </is>
-      </c>
       <c r="M61" s="15" t="inlineStr">
         <is>
-          <t>校了</t>
+          <t>構成案は作成済み</t>
+        </is>
+      </c>
+      <c r="N61" s="15" t="inlineStr">
+        <is>
+          <t>計画書の確定</t>
         </is>
       </c>
     </row>
@@ -5261,58 +6526,64 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>10-7</t>
+          <t>10-6</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>データCD-Rの作成</t>
+          <t>印刷・製本</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>成果品①〜⑥のデータ</t>
-        </is>
-      </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>仕様書4 成果品</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
+          <t>計画書50部、概要版50部。色校正を含む</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品⑤・仕様書4 成果品⑥</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度
+【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="H62" s="16" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I62" s="20" t="inlineStr">
+      <c r="J62" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J62" s="18" t="n">
+      <c r="K62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K62" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="L62" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>各成果品の確定</t>
+          <t>**逆算表を作成済み。12月までに印刷業者を押さえる必要がある**</t>
+        </is>
+      </c>
+      <c r="N62" s="15" t="inlineStr">
+        <is>
+          <t>校了</t>
         </is>
       </c>
     </row>
@@ -5324,64 +6595,137 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
+          <t>10-7</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>データCD-Rの作成</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>成果品①〜⑥のデータ</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4 成果品</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>【成果品】（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J63" s="20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="K63" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="N63" s="15" t="inlineStr">
+        <is>
+          <t>各成果品の確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>P10 完成・納品</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
           <t>10-8</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>納品・検収</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>令和9年3月31日まで</t>
         </is>
       </c>
-      <c r="E63" s="15" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>仕様書3（業務期間）</t>
         </is>
       </c>
-      <c r="F63" s="16" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>【3】契約締結の日から令和9年3月31日まで</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="H63" s="16" t="inlineStr">
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I63" s="20" t="inlineStr">
+      <c r="J64" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="J63" s="18" t="n">
+      <c r="K64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K63" s="19" t="n">
+      <c r="L64" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="L63" s="15" t="inlineStr">
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M63" s="15" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr">
         <is>
           <t>全成果品の完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M63"/>
-  <conditionalFormatting sqref="J2:J63">
+  <autoFilter ref="A1:N64"/>
+  <conditionalFormatting sqref="K2:K64">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>100</formula>
     </cfRule>
@@ -5390,10 +6734,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,進行中,要対応,データ待ち,未着手"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="K2:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -5408,7 +6752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5488,31 +6832,31 @@
         </is>
       </c>
       <c r="B2" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A2)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A2)</f>
         <v/>
       </c>
       <c r="C2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A2,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A2,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A2,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A2,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A2,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A2)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A2)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A2)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I2" s="16" t="inlineStr">
@@ -5538,31 +6882,31 @@
         </is>
       </c>
       <c r="B3" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A3)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A3)</f>
         <v/>
       </c>
       <c r="C3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A3,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A3,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A3,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A3,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A3,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A3)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A3)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A3)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I3" s="16" t="inlineStr">
@@ -5588,31 +6932,31 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A4)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A4,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A4,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A4,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A4,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A4,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A4)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A4)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A4)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I4" s="16" t="inlineStr">
@@ -5638,31 +6982,31 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A5)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A5,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A5,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A5,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A5,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A5,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A5)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A5)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A5)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I5" s="16" t="inlineStr">
@@ -5688,31 +7032,31 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A6)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A6,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A6,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A6,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A6,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A6,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A6)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A6)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A6)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I6" s="16" t="inlineStr">
@@ -5738,31 +7082,31 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A7)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A7,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A7,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A7,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A7,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A7,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A7)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A7)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A7)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I7" s="16" t="inlineStr">
@@ -5788,31 +7132,31 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A8)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A8,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A8,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A8,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A8,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A8,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A8)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A8)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A8)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I8" s="16" t="inlineStr">
@@ -5838,31 +7182,31 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A9)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A9,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A9,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A9,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A9,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A9,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A9)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A9)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A9)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I9" s="16" t="inlineStr">
@@ -5888,31 +7232,31 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A10)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A10,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A10,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A10,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A10,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A10,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H10" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A10)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A10)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A10)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I10" s="16" t="inlineStr">
@@ -5938,31 +7282,31 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('01_WBS'!$A$2:$A$63,$A11)</f>
+        <f>COUNTIF('01_WBS'!$A$2:$A$64,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A11,'01_WBS'!$I$2:$I$63,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"完了")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A11,'01_WBS'!$I$2:$I$63,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"進行中")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A11,'01_WBS'!$I$2:$I$63,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"要対応")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A11,'01_WBS'!$I$2:$I$63,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$63,$A11,'01_WBS'!$I$2:$I$63,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"未着手")</f>
         <v/>
       </c>
       <c r="H11" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A11)*'01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A11)*'01_WBS'!$J$2:$J$63*'01_WBS'!$K$2:$K$63)/SUMPRODUCT(('01_WBS'!$A$2:$A$63=$A11)*'01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I11" s="16" t="inlineStr">
@@ -6012,7 +7356,7 @@
         <v/>
       </c>
       <c r="H12" s="26">
-        <f>IF(SUM('01_WBS'!$K$2:$K$63)=0,0,SUMPRODUCT('01_WBS'!$J$2:$J$63,'01_WBS'!$K$2:$K$63)/SUM('01_WBS'!$K$2:$K$63)/100)</f>
+        <f>IF(SUM('01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT('01_WBS'!$K$2:$K$64,'01_WBS'!$L$2:$L$64)/SUM('01_WBS'!$L$2:$L$64)/100)</f>
         <v/>
       </c>
       <c r="I12" s="16" t="inlineStr">
@@ -6036,6 +7380,13 @@
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>※ 各作業が仕様書のどの条項にあたるかは 01_WBS のE列・F列、条項の網羅状況は 09_仕様書対応表 を参照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>※ 01_WBS の「状態」「進捗率」を書き換えると、本表とダッシュボードが再計算されます。</t>
         </is>
@@ -6418,7 +7769,7 @@
           <t>受託者</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -6445,7 +7796,7 @@
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7003,7 +8354,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7035,7 +8386,7 @@
           <t>町</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7478,7 +8829,7 @@
           <t>町の認定台帳による確認（依頼票N1〜N4）。確認までは前提の異なる2ケースで算定する</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7508,7 +8859,7 @@
           <t>依頼票を1便で送付する。最優先7項目は8月中の回答を求める</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7538,7 +8889,7 @@
           <t>受託者案（4回）を提示して町と確定する（依頼票C4）</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7568,7 +8919,7 @@
           <t>町の事業実績（令和3〜7年度）で代替する（依頼票H3）</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
@@ -7887,7 +9238,7 @@
           <t>仕様書3</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -7917,7 +9268,7 @@
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
@@ -8007,7 +9358,7 @@
           <t>仕様書8①（受託者が作成し相互確認）</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260813.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260813.xlsx
@@ -17,9 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_課題・リスク" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_変更管理・打合せ記録" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_仕様書対応表" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ブロック別進捗" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$N$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_WBS'!$A$1:$O$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -597,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -896,403 +897,369 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
+          <t>■ 仕様書の業務ブロック別</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>仕様書ブロック</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>作業数</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>加重進捗率</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>現況・律速</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6">
+        <f>'10_ブロック別進捗'!A2</f>
+        <v/>
+      </c>
+      <c r="B20" s="7">
+        <f>'10_ブロック別進捗'!C2</f>
+        <v/>
+      </c>
+      <c r="C20" s="8">
+        <f>'10_ブロック別進捗'!I2</f>
+        <v/>
+      </c>
+      <c r="D20" s="9">
+        <f>'10_ブロック別進捗'!J2</f>
+        <v/>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6">
+        <f>'10_ブロック別進捗'!A3</f>
+        <v/>
+      </c>
+      <c r="B21" s="7">
+        <f>'10_ブロック別進捗'!C3</f>
+        <v/>
+      </c>
+      <c r="C21" s="8">
+        <f>'10_ブロック別進捗'!I3</f>
+        <v/>
+      </c>
+      <c r="D21" s="9">
+        <f>'10_ブロック別進捗'!J3</f>
+        <v/>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6">
+        <f>'10_ブロック別進捗'!A4</f>
+        <v/>
+      </c>
+      <c r="B22" s="7">
+        <f>'10_ブロック別進捗'!C4</f>
+        <v/>
+      </c>
+      <c r="C22" s="8">
+        <f>'10_ブロック別進捗'!I4</f>
+        <v/>
+      </c>
+      <c r="D22" s="9">
+        <f>'10_ブロック別進捗'!J4</f>
+        <v/>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6">
+        <f>'10_ブロック別進捗'!A5</f>
+        <v/>
+      </c>
+      <c r="B23" s="7">
+        <f>'10_ブロック別進捗'!C5</f>
+        <v/>
+      </c>
+      <c r="C23" s="8">
+        <f>'10_ブロック別進捗'!I5</f>
+        <v/>
+      </c>
+      <c r="D23" s="9">
+        <f>'10_ブロック別進捗'!J5</f>
+        <v/>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6">
+        <f>'10_ブロック別進捗'!A6</f>
+        <v/>
+      </c>
+      <c r="B24" s="7">
+        <f>'10_ブロック別進捗'!C6</f>
+        <v/>
+      </c>
+      <c r="C24" s="8">
+        <f>'10_ブロック別進捗'!I6</f>
+        <v/>
+      </c>
+      <c r="D24" s="9">
+        <f>'10_ブロック別進捗'!J6</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6">
+        <f>'10_ブロック別進捗'!A7</f>
+        <v/>
+      </c>
+      <c r="B25" s="7">
+        <f>'10_ブロック別進捗'!C7</f>
+        <v/>
+      </c>
+      <c r="C25" s="8">
+        <f>'10_ブロック別進捗'!I7</f>
+        <v/>
+      </c>
+      <c r="D25" s="9">
+        <f>'10_ブロック別進捗'!J7</f>
+        <v/>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6">
+        <f>'10_ブロック別進捗'!A8</f>
+        <v/>
+      </c>
+      <c r="B26" s="7">
+        <f>'10_ブロック別進捗'!C8</f>
+        <v/>
+      </c>
+      <c r="C26" s="8">
+        <f>'10_ブロック別進捗'!I8</f>
+        <v/>
+      </c>
+      <c r="D26" s="9">
+        <f>'10_ブロック別進捗'!J8</f>
+        <v/>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6">
+        <f>'10_ブロック別進捗'!A9</f>
+        <v/>
+      </c>
+      <c r="B27" s="7">
+        <f>'10_ブロック別進捗'!C9</f>
+        <v/>
+      </c>
+      <c r="C27" s="8">
+        <f>'10_ブロック別進捗'!I9</f>
+        <v/>
+      </c>
+      <c r="D27" s="9">
+        <f>'10_ブロック別進捗'!J9</f>
+        <v/>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6">
+        <f>'10_ブロック別進捗'!A10</f>
+        <v/>
+      </c>
+      <c r="B28" s="7">
+        <f>'10_ブロック別進捗'!C10</f>
+        <v/>
+      </c>
+      <c r="C28" s="8">
+        <f>'10_ブロック別進捗'!I10</f>
+        <v/>
+      </c>
+      <c r="D28" s="9">
+        <f>'10_ブロック別進捗'!J10</f>
+        <v/>
+      </c>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6">
+        <f>'10_ブロック別進捗'!A11</f>
+        <v/>
+      </c>
+      <c r="B29" s="7">
+        <f>'10_ブロック別進捗'!C11</f>
+        <v/>
+      </c>
+      <c r="C29" s="8">
+        <f>'10_ブロック別進捗'!I11</f>
+        <v/>
+      </c>
+      <c r="D29" s="9">
+        <f>'10_ブロック別進捗'!J11</f>
+        <v/>
+      </c>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6">
+        <f>'10_ブロック別進捗'!A12</f>
+        <v/>
+      </c>
+      <c r="B30" s="7">
+        <f>'10_ブロック別進捗'!C12</f>
+        <v/>
+      </c>
+      <c r="C30" s="8">
+        <f>'10_ブロック別進捗'!I12</f>
+        <v/>
+      </c>
+      <c r="D30" s="9">
+        <f>'10_ブロック別進捗'!J12</f>
+        <v/>
+      </c>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
           <t>■ 現況</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>見える化システムによる分析は12分野135ファイルを取り込み、実質的に完了した。認定者数は平成19年3月末〜令和8年3月末の20期分を、要介護度別・年齢階層別・被保険者区分別で確定させた。</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>成果品6件のうち3件（①第5版・③第3版・④第2版）が初稿段階に達し、②は算定シートの構築まで進んだ。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>**一方、町からの実績データは35項目すべてが未受領で、サービス見込量推計・保険料算定・第9期評価の確定はいずれも着手できない。**</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>**最大の律速は令和8年3月末の認定者数である。**見える化システムの値は792人で、20期の系列で唯一の大幅減（▲152人・▲16.1％）。県内59市町村で認定率が2.0ポイント以上下がったのは小野町のみで、4.3σの外れ値にあたる。減少の77.0％が85歳以上に集中しており、確定値が792人か900人台かで給付費は2割近く動く。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>令和7年度調査の結果は集計結果・分析報告書として取りまとめ、素案第2版に反映した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の92.9％が需要側の要因で、供給制約は0.6％であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替えた。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>算定シート・成果指標の目標値案・データ依頼票・業務設計書を作成し、認定者数の確定を待たずにできる準備は概ね終えた。**値が入れば給付費と保険料まで一気に通る状態にしてある。**</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>■ 警戒事項</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>影響</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="n">
+    <row r="42">
+      <c r="A42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>令和8年3月末の認定者数が県内唯一の外れ値</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>認定者推計・給付費推計・保険料算定のすべてが確定できない</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>町の認定台帳による確認（依頼票N1〜N4）。確認までは前提の異なる2ケース（C1・C2）で算定する</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>町の実績データが35項目すべて未受領</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>第9期の評価、成果指標の現状値、見込量、保険料のいずれも確定できない</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>依頼票を1便で送付する。最優先7項目は8月中の回答を求める</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>高齢者福祉サービス推進協議会の開催回数・時期が未定</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>工程が引けず、パブリックコメント・印刷の日程も確定できない</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>**仕様書に回数の指定がない。**受託者案（4回）を提示して町と確定する（依頼票C4）</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>通いの場の実態が把握できていない</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>第9期の介護予防施策を評価できず、第10期の最重点施策も設計できない</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>見える化は0か所、調査は週1回以上5.5％（約190人規模）。町の事業実績で確認する（依頼票H3）</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>印刷工程が確保されていない</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>計画書50部・概要版50部が納期に間に合わない</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>令和9年2月下旬の校了から逆算し、12月までに印刷業者を押さえる</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>見える化システムへの入力作業が未着手</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>出力の分析だけでは仕様書4(2)を満たさない</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>アカウント・権限・作業範囲・時期を町と確認する（依頼票C5）</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>■ 直近のマイルストーン</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>時期</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>令和8年8月中</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>町データ依頼票の送付（最優先7項目）</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>令和8年8〜9月</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>協議会 第1回（第9期の評価・調査結果）</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>要対応</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>**開催日が未定**</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>令和8年9月</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>町からの認定者数の回答</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>町の照会</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>令和8年10月</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>**認定者数の確定 → 見込量の推計 → 見える化への入力**</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>認定者数の確認</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>令和8年11月</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>保険料のケース別算定、協議会 第2回</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>見込量の確定</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>令和8年12月</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>素案の確定、協議会 第3回</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>保険料の算定</t>
         </is>
       </c>
       <c r="E42" s="9" t="n"/>
@@ -1301,24 +1268,22 @@
       <c r="H42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>令和9年1月</t>
-        </is>
+      <c r="A43" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>パブリックコメント（1か月）</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>町の実績データが35項目すべて未受領</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>第9期の評価、成果指標の現状値、見込量、保険料のいずれも確定できない</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>依頼票を1便で送付する。最優先7項目は8月中の回答を求める</t>
         </is>
       </c>
       <c r="E43" s="9" t="n"/>
@@ -1327,24 +1292,22 @@
       <c r="H43" s="9" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>令和9年2月下旬</t>
-        </is>
+      <c r="A44" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>**計画書の校了・下版（動かせない期限）**</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>高齢者福祉サービス推進協議会の開催回数・時期が未定</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>工程が引けず、パブリックコメント・印刷の日程も確定できない</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>パブコメ対応</t>
+          <t>**仕様書に回数の指定がない。**受託者案（4回）を提示して町と確定する（依頼票C4）</t>
         </is>
       </c>
       <c r="E44" s="9" t="n"/>
@@ -1353,30 +1316,339 @@
       <c r="H44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
-        <is>
-          <t>令和9年3月31日</t>
-        </is>
+      <c r="A45" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>納品（業務期間の末日）</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>通いの場の実態が把握できていない</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>第9期の介護予防施策を評価できず、第10期の最重点施策も設計できない</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>全成果品の完成</t>
+          <t>見える化は0か所、調査は週1回以上5.5％（約190人規模）。町の事業実績で確認する（依頼票H3）</t>
         </is>
       </c>
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n"/>
       <c r="H45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>印刷工程が確保されていない</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>計画書50部・概要版50部が納期に間に合わない</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>令和9年2月下旬の校了から逆算し、12月までに印刷業者を押さえる</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>見える化システムへの入力作業が未着手</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>出力の分析だけでは仕様書4(2)を満たさない</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>アカウント・権限・作業範囲・時期を町と確認する（依頼票C5）</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>■ 直近のマイルストーン</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>令和8年8月中</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>町データ依頼票の送付（最優先7項目）</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>令和8年8〜9月</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>協議会 第1回（第9期の評価・調査結果）</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>**開催日が未定**</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>令和8年9月</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>町からの認定者数の回答</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>町の照会</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+      <c r="H53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>令和8年10月</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>**認定者数の確定 → 見込量の推計 → 見える化への入力**</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>認定者数の確認</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>令和8年11月</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>保険料のケース別算定、協議会 第2回</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>見込量の確定</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>令和8年12月</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>素案の確定、協議会 第3回</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>保険料の算定</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>令和9年1月</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>パブリックコメント（1か月）</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>素案の確定</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>令和9年2月下旬</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>**計画書の校了・下版（動かせない期限）**</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>パブコメ対応</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>令和9年3月31日</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>納品（業務期間の末日）</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>全成果品の完成</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1823,11 +2095,12 @@
 4-2 集計データの整理
 4-3 集計結果・分析報告書の作成
 4-4 クロス集計の設計
-4-5 個票によるクロス集計</t>
+4-5 個票によるクロス集計
+4-6 レッドチームレビュー</t>
         </is>
       </c>
       <c r="E14" s="16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
@@ -2334,29 +2607,661 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>仕様書ブロック</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>該当条項</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>作業数</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>要対応</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>加重進捗率</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>現況・律速</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>B1 現状分析（基礎データ・資料の整理分析）</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>4(1)</t>
+        </is>
+      </c>
+      <c r="C2" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E2" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F2" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G2" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H2" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A2,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I2" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A2)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J2" s="15" t="inlineStr">
+        <is>
+          <t>第9期計画・第3期地域福祉計画の確認は完了。町からの実績データが未受領</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>4(1)①ア、4(1)①イ、4(1)①ウ、4(1)①エ、4(1)①オ</t>
+        </is>
+      </c>
+      <c r="C3" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A3)</f>
+        <v/>
+      </c>
+      <c r="D3" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E3" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F3" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G3" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H3" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A3,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I3" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A3)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J3" s="15" t="inlineStr">
+        <is>
+          <t>**認定者数の20期系列は確定。令和8年3月末の値の確認と、介護予防（総合事業・通いの場）のデータ欠落が残る**</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>B3 介護保険給付費等の分析</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>4(1)②</t>
+        </is>
+      </c>
+      <c r="C4" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A4)</f>
+        <v/>
+      </c>
+      <c r="D4" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E4" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F4" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G4" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H4" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A4,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I4" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A4)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>成果品①は第5版。町の給付実績で数値を確定する段階</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>4(1)③</t>
+        </is>
+      </c>
+      <c r="C5" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A5)</f>
+        <v/>
+      </c>
+      <c r="D5" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G5" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H5" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A5,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A5)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>**単純集計は完了。個票がないとクロス集計17件ができない**</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>4(2)</t>
+        </is>
+      </c>
+      <c r="C6" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G6" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H6" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A6,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I6" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A6)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>**算定シートとケース設定は完了。推計・算定そのものは認定者数の確定待ちで着手できない**</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>4(3)</t>
+        </is>
+      </c>
+      <c r="C7" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A7,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I7" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A7)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>骨子案第3版・素案第2版・成果指標の目標値案まで到達。見込量と保険料の反映が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>B7 最終調整及び計画書の作成</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>4(4)</t>
+        </is>
+      </c>
+      <c r="C8" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G8" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H8" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A8,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I8" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A8)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>パブリックコメント後に着手する。時期が来ていない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>4(5)</t>
+        </is>
+      </c>
+      <c r="C9" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H9" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A9,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I9" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A9)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>**資料と様式は揃っている。協議会の開催回数・時期が未定で工程が引けない**</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>成果品①、成果品②、成果品③、成果品④、成果品⑤、成果品⑥ ほか</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H10" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A10,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I10" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A10)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J10" s="15" t="inlineStr">
+        <is>
+          <t>**製本・印刷が納品仕様に含まれる。令和9年2月下旬の校了が動かせない期限**</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>1、2(1)、2(2)、2(3)、3、5(1) ほか</t>
+        </is>
+      </c>
+      <c r="C11" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A11,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I11" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A11)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>仕様書の適合性チェック・データ依頼票は完了。工程と協議会日程の合意が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>B11 仕様書に定めのない作業</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>（該当条項なし）</t>
+        </is>
+      </c>
+      <c r="C12" s="16">
+        <f>COUNTIF('01_WBS'!$E$2:$E$64,$A12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"完了")</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"進行中")</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"要対応")</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>COUNTIFS('01_WBS'!$E$2:$E$64,$A12,'01_WBS'!$K$2:$K$64,"未着手")</f>
+        <v/>
+      </c>
+      <c r="I12" s="23">
+        <f>IF(SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$M$2:$M$64)=0,"―",SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$E$2:$E$64=$A12)*'01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>該当なし。仕様書のいずれかの条項に紐づかない作業が発生した場合はここに現れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr"/>
+      <c r="C13" s="25">
+        <f>SUM(C2:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="25">
+        <f>SUM(D2:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="25">
+        <f>SUM(E2:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="25">
+        <f>SUM(F2:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="25">
+        <f>SUM(G2:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="25">
+        <f>SUM(H2:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="26">
+        <f>IF(SUM('01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$64,'01_WBS'!$M$2:$M$64)/SUM('01_WBS'!$M$2:$M$64)/100)</f>
+        <v/>
+      </c>
+      <c r="J13" s="15" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>※ 段階（02_段階サマリ）は業務の進み方の切り口、ブロックは委託契約上の業務単位の切り口です。同じ作業を別の軸で見ています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>※ 作業が複数の条項にまたがる場合は、先頭の条項が属するブロックに数えています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>※ 未分類の作業があります：[]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="64" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2382,50 +3287,55 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
+          <t>仕様書ブロック</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
           <t>仕様書 条項</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>仕様書の記載内容（原文）</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>担当</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>予定開始</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>予定完了</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>進捗率</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>重み</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>実績・根拠</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>前提条件・ブロッカー</t>
         </is>
@@ -2452,48 +3362,53 @@
           <t>実施体制、役割分担、連絡系統</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>公告10⑥（技術者の配置）</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>【公告10⑥】研究員は「見える化」システムやニーズ調査など各種データから介護給付費の統計分析により将来のサービス量を推計し計画化できる者（公告第1-19号 10⑥）</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K2" s="18" t="n">
+      <c r="L2" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L2" s="19" t="n">
+      <c r="M2" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>キックオフ資料・業務計画書（02_キックオフ・業務計画）</t>
         </is>
       </c>
-      <c r="N2" s="15" t="inlineStr">
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2520,48 +3435,53 @@
           <t>前受託者からの引継ぎ資料の棚卸しと索引化</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>仕様書全般</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="K3" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K3" s="18" t="n">
+      <c r="L3" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L3" s="19" t="n">
+      <c r="M3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="15" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>manifest_全ファイル（207ファイル）</t>
         </is>
       </c>
-      <c r="N3" s="15" t="inlineStr">
+      <c r="O3" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2588,48 +3508,53 @@
           <t>原典4件（公告・仕様書×2計画）を読み、成果品要件・工程・作業分担を確定</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>仕様書全般</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>【全般】委託仕様書及び公告の全体（成果品要件・工程・作業分担の確認）</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="L4" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L4" s="19" t="n">
+      <c r="M4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>仕様書適合性チェック 第2版（00_引継ぎ）。初版8/3、第2版8/13</t>
         </is>
       </c>
-      <c r="N4" s="15" t="inlineStr">
+      <c r="O4" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2656,48 +3581,53 @@
           <t>5章構成・基本理念・3基本目標・14施策、標準給付費3,566,486千円、保険料6,600円の算定根拠</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>B1 現状分析（基礎データ・資料の整理分析）</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>【4(1)】基礎的な地域データ及び資料の整理分析（現状分析）。高齢者福祉・介護保険をめぐる施策の動向、小野町の概要及び社会経済的特性、地域福祉資源の整備状況、高齢者の現況動向及びサービスの利用状況等について、小野町が提供するデータをもとに整理分析を行う。（計画策定の検討資料として活用するため、各種事項の将来推計を行う。なお、推計にあたっては、可能な限り細分化する）</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="L5" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L5" s="19" t="n">
+      <c r="M5" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>第9期計画本文（13_関連計画）。骨子案第3版・成果品①第5版に反映</t>
         </is>
       </c>
-      <c r="N5" s="15" t="inlineStr">
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2724,48 +3654,53 @@
           <t>重複5施策を特定。成年後見は移管、虐待防止・災害対応・支え合いは連携</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>仕様書2(2)</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>【2(2)】国が示す第10期計画に関する基本的な考え方を踏まえた上で、本町の特性を活かした計画とする。</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="L6" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L6" s="19" t="n">
+      <c r="M6" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>地域福祉計画との整合確認メモ（03_計画素案）</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="O6" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2792,48 +3727,53 @@
           <t>依頼35項目＋確認事項12件。基準日・年度範囲・単位・様式まで指定</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>仕様書5(1)（資料は町が貸与）</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>【5(1)】本業務の実施に必要な資料等は、小野町が受託者に貸与するものとする。</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="L7" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="19" t="n">
+      <c r="M7" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="15" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>小野町_データ依頼票（16_町データ依頼）</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr">
+      <c r="O7" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -2860,48 +3800,53 @@
           <t>依頼票に基づく資料・データの受領</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>仕様書5(1)</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>【5(1)】本業務の実施に必要な資料等は、小野町が受託者に貸与するものとする。</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K8" s="18" t="n">
+      <c r="L8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="19" t="n">
+      <c r="M8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="N8" s="15" t="inlineStr">
         <is>
           <t>受領0件／依頼35件</t>
         </is>
       </c>
-      <c r="N8" s="15" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t>**町の回答。P5・P7・P8のほぼ全てがこれに依存する**</t>
         </is>
@@ -2928,48 +3873,53 @@
           <t>高齢者計画の仕様書には工程表がないため、業務期間から逆算した工程と協議会の回数・時期を町と合意する。あわせて仕様書の疑義4件を照会する</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>仕様書5(3)</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>【5(3)】本仕様書に定めのない事項及び疑義が生じた場合は、小野町と受託者で協議するものとする。</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="L9" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="L9" s="19" t="n">
+      <c r="M9" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="15" t="inlineStr">
+      <c r="N9" s="15" t="inlineStr">
         <is>
           <t>**工程変更協議資料と確認事項12件を作成済み（うち高齢者に係るもの8件）**</t>
         </is>
       </c>
-      <c r="N9" s="15" t="inlineStr">
+      <c r="O9" s="15" t="inlineStr">
         <is>
           <t>**町との協議。協議会の回数が決まらないとP6・P8・P9・P10の日程が引けない**</t>
         </is>
@@ -2996,48 +3946,53 @@
           <t>総人口、高齢化率、前期・後期高齢者、世帯。令和32年まで推計</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①ア</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>【4(1)①ア】統計分析（ア）人口</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="K10" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="L10" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L10" s="19" t="n">
+      <c r="M10" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>基礎数値整理ブック（A系13ファイル）</t>
         </is>
       </c>
-      <c r="N10" s="15" t="inlineStr">
+      <c r="O10" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3064,48 +4019,53 @@
           <t>被保険者数の推移と推計</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①ア</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>【4(1)①ア】統計分析（ア）人口</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="L11" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L11" s="19" t="n">
+      <c r="M11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="15" t="inlineStr">
+      <c r="N11" s="15" t="inlineStr">
         <is>
           <t>B系4ファイル</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr">
+      <c r="O11" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3132,48 +4092,53 @@
           <t>平成19年3月末〜令和8年3月末の20期。要介護度別7区分・年齢階層別・被保険者区分別</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①イ</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>【4(1)①イ】統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="L12" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L12" s="19" t="n">
+      <c r="M12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>要支援要介護認定者数の整理（07_見える化整理・10シート）。第1号＋第2号＝全体を20期で検算済み</t>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="O12" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3200,48 +4165,53 @@
           <t>令和8年3月末の▲152人（▲16.1％）の要因分析。県内59市町村との比較</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①イ</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>【4(1)①イ】統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="L13" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="L13" s="19" t="n">
+      <c r="M13" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="15" t="inlineStr">
+      <c r="N13" s="15" t="inlineStr">
         <is>
           <t>**減少の77.0％が85歳以上に集中。県内で唯一4.3σの外れ値。**3出典を基準日順に配列し、令和7年7月まで一貫増加を確認</t>
         </is>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="O13" s="15" t="inlineStr">
         <is>
           <t>**町の認定台帳による確認（依頼票N1〜N4）。本業務の最大の律速**</t>
         </is>
@@ -3268,48 +4238,53 @@
           <t>居宅・施設・地域密着型の受給者数</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①ウ</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>【4(1)①ウ】統計分析（ウ）居宅サービス・施設サービス・地域密着型サービスの受給者数</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K14" s="18" t="n">
+      <c r="L14" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L14" s="19" t="n">
+      <c r="M14" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t>地域分析ブック（D1〜D4、D32系）</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="O14" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3336,48 +4311,53 @@
           <t>総合事業対象者、通いの場参加者</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①エ</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>【4(1)①エ】統計分析（エ）介護予防事業対象者数</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="L15" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="L15" s="19" t="n">
+      <c r="M15" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M15" s="15" t="inlineStr">
+      <c r="N15" s="15" t="inlineStr">
         <is>
           <t>**見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr">
+      <c r="O15" s="15" t="inlineStr">
         <is>
           <t>**町の事業実績（依頼票H3）。見える化の0か所と調査の5.5％が整合しない**</t>
         </is>
@@ -3404,49 +4384,54 @@
           <t>認知症高齢者の日常生活自立度、認知症施策の実施状況</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①イ・2(3)</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>【4(1)①イ】統計分析（イ）要支援者数、要介護認定者数、認知症高齢者数
 【2(3)】国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="K16" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="L16" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="L16" s="19" t="n">
+      <c r="M16" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M16" s="15" t="inlineStr">
+      <c r="N16" s="15" t="inlineStr">
         <is>
           <t>J16〜J18を取得。自立度Ⅱa 68→148人、M 7→29人</t>
         </is>
       </c>
-      <c r="N16" s="15" t="inlineStr">
+      <c r="O16" s="15" t="inlineStr">
         <is>
           <t>研修系（J1〜J15）は本町の値が未公表。町の実績で代替する（依頼票H9）</t>
         </is>
@@ -3473,48 +4458,53 @@
           <t>県内59市町村との比較。自給率67.57％</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①オ</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>【4(1)①オ】統計分析（オ）その他計画策定に必要な推計</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="L17" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L17" s="19" t="n">
+      <c r="M17" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="15" t="inlineStr">
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>δ2・δ3系12指標</t>
         </is>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3541,48 +4531,53 @@
           <t>歳入歳出、基金、繰越金</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="K18" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K18" s="18" t="n">
+      <c r="L18" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="L18" s="19" t="n">
+      <c r="M18" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="15" t="inlineStr">
+      <c r="N18" s="15" t="inlineStr">
         <is>
           <t>財政整理ブック（D47・D48系25指標、H26〜R5）。繰越金182.0百万円・基金純増88.1百万円</t>
         </is>
       </c>
-      <c r="N18" s="15" t="inlineStr">
+      <c r="O18" s="15" t="inlineStr">
         <is>
           <t>令和6・7年度の決算（依頼票S7）。年報ベースのためR6・R7が未反映</t>
         </is>
@@ -3609,48 +4604,53 @@
           <t>在宅医療・介護連携、医療提供体制、リハビリ提供体制、保険者機能強化推進交付金の評価指標</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>B2 統計分析</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)①オ</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>【4(1)①オ】統計分析（オ）その他計画策定に必要な推計</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K19" s="18" t="n">
+      <c r="L19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="19" t="n">
+      <c r="M19" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" s="15" t="inlineStr">
+      <c r="N19" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr">
+      <c r="O19" s="15" t="inlineStr">
         <is>
           <t>見える化システムへのアクセス</t>
         </is>
@@ -3677,49 +4677,54 @@
           <t>サービス費目ごとの給付費・地域支援事業の分析、制度改正の影響</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>B3 介護保険給付費等の分析</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)②・成果品①</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
 【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="H20" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="K20" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K20" s="18" t="n">
+      <c r="L20" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="L20" s="19" t="n">
+      <c r="M20" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="M20" s="15" t="inlineStr">
+      <c r="N20" s="15" t="inlineStr">
         <is>
           <t>**第5版（8章・44表・約29,500字）。**第9期計画との対比、施策体系との対応、認定者数20期系列と年齢階層別分解、令和7年度調査による検証まで整理</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr">
+      <c r="O20" s="15" t="inlineStr">
         <is>
           <t>町の給付実績（依頼票S1・S2）で数値を確定する</t>
         </is>
@@ -3746,48 +4751,53 @@
           <t>見える化システムの値と町の給付実績の突合</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>B3 介護保険給付費等の分析</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)②</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="H21" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="L21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="19" t="n">
+      <c r="M21" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M21" s="15" t="inlineStr">
+      <c r="N21" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N21" s="15" t="inlineStr">
+      <c r="O21" s="15" t="inlineStr">
         <is>
           <t>町の給付実績（依頼票S1・S2）</t>
         </is>
@@ -3814,48 +4824,53 @@
           <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品①</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>【成果品①】（1）介護保険給付費等分析結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K22" s="18" t="n">
+      <c r="L22" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="M22" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="15" t="inlineStr">
+      <c r="N22" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N22" s="15" t="inlineStr">
+      <c r="O22" s="15" t="inlineStr">
         <is>
           <t>報告書の確定</t>
         </is>
@@ -3882,48 +4897,53 @@
           <t>令和8年3月・104頁の報告書の内容確認と妥当性の検証</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J23" s="17" t="inlineStr">
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K23" s="18" t="n">
+      <c r="L23" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L23" s="19" t="n">
+      <c r="M23" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M23" s="15" t="inlineStr">
+      <c r="N23" s="15" t="inlineStr">
         <is>
           <t>単純集計とリスク分析（年齢階層別・男女別・認定状況別）を取得。報告書内の不整合3件を指摘</t>
         </is>
       </c>
-      <c r="N23" s="15" t="inlineStr">
+      <c r="O23" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -3950,48 +4970,53 @@
           <t>リスク10項目×9区分の保持</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="H24" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J24" s="17" t="inlineStr">
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K24" s="18" t="n">
+      <c r="L24" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L24" s="19" t="n">
+      <c r="M24" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M24" s="15" t="inlineStr">
+      <c r="N24" s="15" t="inlineStr">
         <is>
           <t>集計データ整理ブック（14_アンケート集計・9シート）</t>
         </is>
       </c>
-      <c r="N24" s="15" t="inlineStr">
+      <c r="O24" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4018,48 +5043,53 @@
           <t>単純集計、リスク分析、前回対比、8つの分析、第9期課題への到達状況、第10期への示唆</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="H25" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="I25" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="J25" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J25" s="17" t="inlineStr">
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K25" s="18" t="n">
+      <c r="L25" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L25" s="19" t="n">
+      <c r="M25" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M25" s="15" t="inlineStr">
+      <c r="N25" s="15" t="inlineStr">
         <is>
           <t>**7章・72表・約27,800字（14_アンケート集計）**</t>
         </is>
       </c>
-      <c r="N25" s="15" t="inlineStr">
+      <c r="O25" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4086,48 +5116,53 @@
           <t>前回計画の課題に基づくクロス集計25件の設計</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="G26" s="15" t="inlineStr">
         <is>
           <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K26" s="18" t="n">
+      <c r="L26" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="M26" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M26" s="15" t="inlineStr">
+      <c r="N26" s="15" t="inlineStr">
         <is>
           <t>クロス集計設計書（8シート・25件）。4件掲載済、17件が個票を要し、4件は設問なし</t>
         </is>
       </c>
-      <c r="N26" s="15" t="inlineStr">
+      <c r="O26" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4154,48 +5189,53 @@
           <t>要介護度別・世帯構成別のクロス集計17件</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)③</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="K27" s="18" t="n">
+      <c r="L27" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="19" t="n">
+      <c r="M27" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M27" s="15" t="inlineStr">
+      <c r="N27" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr">
+      <c r="O27" s="15" t="inlineStr">
         <is>
           <t>**令和7年度調査の個票データ（依頼票H16）。地区情報の有無も要確認**</t>
         </is>
@@ -4222,48 +5262,53 @@
           <t>集計・分析の反証検証</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>B4 令和7年度調査結果の反映</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>仕様書4(1)③</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>【4(1)③】介護予防・日常生活圏域ニーズ調査、在宅介護実態調査結果の反映。令和7年度に実施した調査結果を反映させる。</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="I28" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="J28" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J28" s="17" t="inlineStr">
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K28" s="18" t="n">
+      <c r="L28" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L28" s="19" t="n">
+      <c r="M28" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M28" s="15" t="inlineStr">
+      <c r="N28" s="15" t="inlineStr">
         <is>
           <t>REDTEAM 2本（14_アンケート集計）。数値の取り違え1件を自己検出し修正</t>
         </is>
       </c>
-      <c r="N28" s="15" t="inlineStr">
+      <c r="O28" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4290,49 +5335,54 @@
           <t>第9期が第5章2(2)で自ら定める4点検項目に沿って評価</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>B3 介護保険給付費等の分析</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)②・4(5)</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="G29" s="15" t="inlineStr">
         <is>
           <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。
 【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="H29" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="I29" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J29" s="17" t="inlineStr">
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K29" s="18" t="n">
+      <c r="L29" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L29" s="19" t="n">
+      <c r="M29" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M29" s="15" t="inlineStr">
+      <c r="N29" s="15" t="inlineStr">
         <is>
           <t>**協議会資料（08_協議会資料・42表・約23,500字）**</t>
         </is>
       </c>
-      <c r="N29" s="15" t="inlineStr">
+      <c r="O29" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4359,48 +5409,53 @@
           <t>第9期の見込みと実績の対比</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>B3 介護保険給付費等の分析</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)②</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
         <is>
           <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="H30" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J30" s="22" t="inlineStr">
+      <c r="K30" s="22" t="inlineStr">
         <is>
           <t>データ待ち</t>
         </is>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="L30" s="18" t="n">
         <v>40</v>
       </c>
-      <c r="L30" s="19" t="n">
+      <c r="M30" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M30" s="15" t="inlineStr">
+      <c r="N30" s="15" t="inlineStr">
         <is>
           <t>見込みと実績の対比の枠は作成済み（成果品①第7章7、骨子案 参考1）</t>
         </is>
       </c>
-      <c r="N30" s="15" t="inlineStr">
+      <c r="O30" s="15" t="inlineStr">
         <is>
           <t>町の事業実績・給付実績（依頼票H1〜H15）</t>
         </is>
@@ -4427,48 +5482,53 @@
           <t>第9期は新規整備を行わない方針だが、認知症対応型共同生活介護の定員が27人（38.0％）増</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>B3 介護保険給付費等の分析</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>仕様書4(1)②</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>【4(1)②】介護保険給付費等の分析。介護サービス費目ごとの介護給付費や地域支援事業の利用状況等を分析し、現在の状況や傾向の把握、また、制度改正に伴う影響等を分析し、今後の見通しや具体的施策を検討する。</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="H31" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="I31" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J31" s="20" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K31" s="18" t="n">
+      <c r="L31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="19" t="n">
+      <c r="M31" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M31" s="15" t="inlineStr">
+      <c r="N31" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N31" s="15" t="inlineStr">
+      <c r="O31" s="15" t="inlineStr">
         <is>
           <t>整備の経緯の確認（依頼票H15）</t>
         </is>
@@ -4495,49 +5555,54 @@
           <t>基本課題・施策方向・重点課題・施策体系</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>仕様書4(3)・成果品③</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
 【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="H32" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="I32" s="16" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="J32" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J32" s="19" t="inlineStr">
+      <c r="K32" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K32" s="18" t="n">
+      <c r="L32" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="L32" s="19" t="n">
+      <c r="M32" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M32" s="15" t="inlineStr">
+      <c r="N32" s="15" t="inlineStr">
         <is>
           <t>**第3版（13表・9,241字）。**第9期の5章構成・3基本目標・14施策を反映し、地域福祉計画との重複を精査。第9期の見込みと実績の対比も収載</t>
         </is>
       </c>
-      <c r="N32" s="15" t="inlineStr">
+      <c r="O32" s="15" t="inlineStr">
         <is>
           <t>実績データによる数値の確定</t>
         </is>
@@ -4564,49 +5629,54 @@
           <t>基本理念・基本目標・施策体系の合意</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>仕様書4(3)・4(5)</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
 【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="I33" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J33" s="20" t="inlineStr">
+      <c r="K33" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K33" s="18" t="n">
+      <c r="L33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="19" t="n">
+      <c r="M33" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M33" s="15" t="inlineStr">
+      <c r="N33" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N33" s="15" t="inlineStr">
+      <c r="O33" s="15" t="inlineStr">
         <is>
           <t>**協議会の開催回数・時期が未定（依頼票C4）**</t>
         </is>
@@ -4633,48 +5703,53 @@
           <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品③</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>【成果品③】（3）小野町高齢者保健福祉計画・第10期介護保険事業計画骨子案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="H34" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J34" s="20" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K34" s="18" t="n">
+      <c r="L34" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="19" t="n">
+      <c r="M34" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="15" t="inlineStr">
+      <c r="N34" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N34" s="15" t="inlineStr">
+      <c r="O34" s="15" t="inlineStr">
         <is>
           <t>骨子案の確定</t>
         </is>
@@ -4701,48 +5776,53 @@
           <t>サービス54区分の単価×量から給付費、標準給付費、保険料までを算式でつなぐ</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="H35" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J35" s="17" t="inlineStr">
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K35" s="18" t="n">
+      <c r="L35" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L35" s="19" t="n">
+      <c r="M35" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M35" s="15" t="inlineStr">
+      <c r="N35" s="15" t="inlineStr">
         <is>
           <t>**見込量保険料算定シート（04_算定・見込量・11シート）。**第9期の実数で検算済み（月額6,442円 対 実際6,600円。差2.4％は仮置き値による）</t>
         </is>
       </c>
-      <c r="N35" s="15" t="inlineStr">
+      <c r="O35" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4769,48 +5849,53 @@
           <t>標準（低位・高位）、施設整備あり、制度改正の影響、基金活用、保険料据置の逆算</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="H36" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="I36" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J36" s="17" t="inlineStr">
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K36" s="18" t="n">
+      <c r="L36" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L36" s="19" t="n">
+      <c r="M36" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M36" s="15" t="inlineStr">
+      <c r="N36" s="15" t="inlineStr">
         <is>
           <t>**C1〜C6。引継ぎ時点の3ケースは基金の扱いのみで、仕様書が例示する施設整備・制度改正に対応していなかった**</t>
         </is>
       </c>
-      <c r="N36" s="15" t="inlineStr">
+      <c r="O36" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -4837,48 +5922,53 @@
           <t>人口推計に年齢階層別の認定率を乗じる自然体推計</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="H37" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J37" s="20" t="inlineStr">
+      <c r="K37" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K37" s="18" t="n">
+      <c r="L37" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="19" t="n">
+      <c r="M37" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M37" s="15" t="inlineStr">
+      <c r="N37" s="15" t="inlineStr">
         <is>
           <t>算式は実装済み（03_認定者推計）</t>
         </is>
       </c>
-      <c r="N37" s="15" t="inlineStr">
+      <c r="O37" s="15" t="inlineStr">
         <is>
           <t>**認定者数の確定（2-4）**</t>
         </is>
@@ -4905,48 +5995,53 @@
           <t>サービス種類別の利用者数・量・給付費</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="G38" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I38" s="16" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J38" s="20" t="inlineStr">
+      <c r="K38" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K38" s="18" t="n">
+      <c r="L38" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="19" t="n">
+      <c r="M38" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="M38" s="15" t="inlineStr">
+      <c r="N38" s="15" t="inlineStr">
         <is>
           <t>算式は実装済み（05・06_見込量）</t>
         </is>
       </c>
-      <c r="N38" s="15" t="inlineStr">
+      <c r="O38" s="15" t="inlineStr">
         <is>
           <t>**認定者数の確定（2-4）、町の給付実績（依頼票S1・S2）**</t>
         </is>
@@ -4973,48 +6068,53 @@
           <t>出力の分析だけでなく、システムへの入力が業務に含まれる</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="G39" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H39" s="16" t="inlineStr">
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="I39" s="16" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="J39" s="20" t="inlineStr">
+      <c r="K39" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K39" s="18" t="n">
+      <c r="L39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="19" t="n">
+      <c r="M39" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M39" s="15" t="inlineStr">
+      <c r="N39" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N39" s="15" t="inlineStr">
+      <c r="O39" s="15" t="inlineStr">
         <is>
           <t>**アカウント・権限・作業範囲・時期の確認（依頼票C5）**</t>
         </is>
@@ -5041,48 +6141,53 @@
           <t>ケースC1〜C6ごとの保険料基準額の算定</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>B5 事業量推計・保険料算出・介護財政</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>仕様書4(2)</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>【4(2)】サービス事業量推計、保険料の算出、介護財政の見通しの検討・調整。「見える化」システムを活用したサービス見込量を推計及び保険料の算出を行うこと。（「見える化」システムへの入力作業を含む。）なお、算定にあたっては、新たに介護施設を整備する場合や制度改正により条件が変わる場合等、様々なケースで勘案する必要があるため、想定されるケースごとに保険料の算定を行うものとする。</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I40" s="16" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J40" s="20" t="inlineStr">
+      <c r="K40" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K40" s="18" t="n">
+      <c r="L40" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="19" t="n">
+      <c r="M40" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M40" s="15" t="inlineStr">
+      <c r="N40" s="15" t="inlineStr">
         <is>
           <t>算式は実装済み（09_保険料算定）</t>
         </is>
       </c>
-      <c r="N40" s="15" t="inlineStr">
+      <c r="O40" s="15" t="inlineStr">
         <is>
           <t>見込量の確定、基金残高・所得段階別人数・収納率（依頼票S3〜S5）</t>
         </is>
@@ -5109,48 +6214,53 @@
           <t>成果品②の本体</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品②</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>【成果品②】（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J41" s="20" t="inlineStr">
+      <c r="K41" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K41" s="18" t="n">
+      <c r="L41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="19" t="n">
+      <c r="M41" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M41" s="15" t="inlineStr">
+      <c r="N41" s="15" t="inlineStr">
         <is>
           <t>算定シートが素材。章立ては未作成</t>
         </is>
       </c>
-      <c r="N41" s="15" t="inlineStr">
+      <c r="O41" s="15" t="inlineStr">
         <is>
           <t>見込量・保険料の算定</t>
         </is>
@@ -5177,48 +6287,53 @@
           <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品②</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>【成果品②】（2）サービス見込量推計結果報告書　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="H42" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H42" s="16" t="inlineStr">
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I42" s="16" t="inlineStr">
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J42" s="20" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K42" s="18" t="n">
+      <c r="L42" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="19" t="n">
+      <c r="M42" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M42" s="15" t="inlineStr">
+      <c r="N42" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N42" s="15" t="inlineStr">
+      <c r="O42" s="15" t="inlineStr">
         <is>
           <t>報告書の確定</t>
         </is>
@@ -5245,49 +6360,54 @@
           <t>骨子案を踏まえた計画素案。12施策の本文</t>
         </is>
       </c>
-      <c r="E43" s="16" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>仕様書4(3)・成果品④</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="G43" s="15" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
 【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H43" s="16" t="inlineStr">
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I43" s="16" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="K43" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="K43" s="18" t="n">
+      <c r="L43" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="L43" s="19" t="n">
+      <c r="M43" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="M43" s="15" t="inlineStr">
+      <c r="N43" s="15" t="inlineStr">
         <is>
           <t>**第2版（5章＋資料編・67表・約32,000字）。**12施策すべてに現状と課題・施策の方向・主な事業・成果指標を記載。未確定156箇所を5区分で明示</t>
         </is>
       </c>
-      <c r="N43" s="15" t="inlineStr">
+      <c r="O43" s="15" t="inlineStr">
         <is>
           <t>見込量・保険料（P7）、成果指標の現状値（依頼票H1〜H15）</t>
         </is>
@@ -5314,48 +6434,53 @@
           <t>40指標の目標値案と根拠の型</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>仕様書4(3)</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="G44" s="15" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H44" s="16" t="inlineStr">
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I44" s="16" t="inlineStr">
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J44" s="17" t="inlineStr">
+      <c r="K44" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K44" s="18" t="n">
+      <c r="L44" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L44" s="19" t="n">
+      <c r="M44" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M44" s="15" t="inlineStr">
+      <c r="N44" s="15" t="inlineStr">
         <is>
           <t>**成果指標目標値案（03_計画素案・40指標）。**現状値が未受領の20指標は算定規則として案を置いた</t>
         </is>
       </c>
-      <c r="N44" s="15" t="inlineStr">
+      <c r="O44" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5382,48 +6507,53 @@
           <t>基本的施策12項目との対応表、包含の形式</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>仕様書2(3)</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>【2(3)】国の「認知症施策推進基本計画」に基づく市町村計画も包含する計画とする。</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="H45" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H45" s="16" t="inlineStr">
+      <c r="I45" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I45" s="16" t="inlineStr">
+      <c r="J45" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J45" s="17" t="inlineStr">
+      <c r="K45" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K45" s="18" t="n">
+      <c r="L45" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L45" s="19" t="n">
+      <c r="M45" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M45" s="15" t="inlineStr">
+      <c r="N45" s="15" t="inlineStr">
         <is>
           <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案</t>
         </is>
       </c>
-      <c r="N45" s="15" t="inlineStr">
+      <c r="O45" s="15" t="inlineStr">
         <is>
           <t>町の意思決定（方式A／B）</t>
         </is>
@@ -5450,48 +6580,53 @@
           <t>素案の未確定156箇所の解消</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>仕様書4(3)</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="G46" s="15" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="H46" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I46" s="16" t="inlineStr">
+      <c r="J46" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J46" s="20" t="inlineStr">
+      <c r="K46" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K46" s="18" t="n">
+      <c r="L46" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="19" t="n">
+      <c r="M46" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="M46" s="15" t="inlineStr">
+      <c r="N46" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N46" s="15" t="inlineStr">
+      <c r="O46" s="15" t="inlineStr">
         <is>
           <t>**P7の完了、町データの受領**</t>
         </is>
@@ -5518,49 +6653,54 @@
           <t>素案の内容の合意</t>
         </is>
       </c>
-      <c r="E47" s="16" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>B6 骨子案・素案の作成</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>仕様書4(3)・4(5)</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="G47" s="15" t="inlineStr">
         <is>
           <t>【4(3)】骨子案・素案の作成。これまでの調査結果を踏まえて第10期計画の基本課題や施策方向を整理し、今後の重点課題と施策の目標・体系をとりまとめた計画骨子案、計画素案を作成し、内容の協議を行う。策定にあたっては町総合計画、町地域福祉計画等の既存計画の関連も調整すること。
 【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H47" s="16" t="inlineStr">
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I47" s="16" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="K47" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K47" s="18" t="n">
+      <c r="L47" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L47" s="19" t="n">
+      <c r="M47" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M47" s="15" t="inlineStr">
+      <c r="N47" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N47" s="15" t="inlineStr">
+      <c r="O47" s="15" t="inlineStr">
         <is>
           <t>協議会の開催時期</t>
         </is>
@@ -5587,48 +6727,53 @@
           <t>データCD-R1部＋冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品④</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="G48" s="15" t="inlineStr">
         <is>
           <t>【成果品④】（4）小野町高齢者保健福祉計画・第10期介護保険事業計画素案　※データ（CD-R）1部、冊子（簡易製本）3部</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H48" s="16" t="inlineStr">
+      <c r="I48" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I48" s="16" t="inlineStr">
+      <c r="J48" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J48" s="20" t="inlineStr">
+      <c r="K48" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K48" s="18" t="n">
+      <c r="L48" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L48" s="19" t="n">
+      <c r="M48" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M48" s="15" t="inlineStr">
+      <c r="N48" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N48" s="15" t="inlineStr">
+      <c r="O48" s="15" t="inlineStr">
         <is>
           <t>素案の確定</t>
         </is>
@@ -5655,48 +6800,53 @@
           <t>小野町高齢者福祉サービス推進協議会</t>
         </is>
       </c>
-      <c r="E49" s="16" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="G49" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="H49" s="16" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H49" s="16" t="inlineStr">
+      <c r="I49" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I49" s="16" t="inlineStr">
+      <c r="J49" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J49" s="21" t="inlineStr">
+      <c r="K49" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="K49" s="18" t="n">
+      <c r="L49" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L49" s="19" t="n">
+      <c r="M49" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M49" s="15" t="inlineStr">
+      <c r="N49" s="15" t="inlineStr">
         <is>
           <t>**仕様書に回数の指定がない。**受託者案は4回</t>
         </is>
       </c>
-      <c r="N49" s="15" t="inlineStr">
+      <c r="O49" s="15" t="inlineStr">
         <is>
           <t>**町との協議（依頼票C4）。これが決まらないと工程が引けない**</t>
         </is>
@@ -5723,48 +6873,53 @@
           <t>評価と調査結果の報告</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="H50" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H50" s="16" t="inlineStr">
+      <c r="I50" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I50" s="16" t="inlineStr">
+      <c r="J50" s="16" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J50" s="21" t="inlineStr">
+      <c r="K50" s="21" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="K50" s="18" t="n">
+      <c r="L50" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="L50" s="19" t="n">
+      <c r="M50" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M50" s="15" t="inlineStr">
+      <c r="N50" s="15" t="inlineStr">
         <is>
           <t>**資料は作成済み（08_協議会資料・42表）**</t>
         </is>
       </c>
-      <c r="N50" s="15" t="inlineStr">
+      <c r="O50" s="15" t="inlineStr">
         <is>
           <t>**開催日が未定**</t>
         </is>
@@ -5791,48 +6946,53 @@
           <t>計画の骨格の合意</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F51" s="15" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="H51" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="I51" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="I51" s="16" t="inlineStr">
+      <c r="J51" s="16" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="J51" s="20" t="inlineStr">
+      <c r="K51" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K51" s="18" t="n">
+      <c r="L51" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="19" t="n">
+      <c r="M51" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M51" s="15" t="inlineStr">
+      <c r="N51" s="15" t="inlineStr">
         <is>
           <t>骨子案第3版・成果指標目標値案は作成済み</t>
         </is>
       </c>
-      <c r="N51" s="15" t="inlineStr">
+      <c r="O51" s="15" t="inlineStr">
         <is>
           <t>P7の完了、開催日の確定</t>
         </is>
@@ -5859,48 +7019,53 @@
           <t>素案の合意</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="G52" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="H52" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H52" s="16" t="inlineStr">
+      <c r="I52" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="I52" s="16" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="J52" s="20" t="inlineStr">
+      <c r="K52" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L52" s="19" t="n">
+      <c r="M52" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M52" s="15" t="inlineStr">
+      <c r="N52" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N52" s="15" t="inlineStr">
+      <c r="O52" s="15" t="inlineStr">
         <is>
           <t>素案の確定</t>
         </is>
@@ -5927,48 +7092,53 @@
           <t>実施要領、意見提出様式、意見と町の考え方の対応表</t>
         </is>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="G53" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H53" s="16" t="inlineStr">
+      <c r="I53" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I53" s="16" t="inlineStr">
+      <c r="J53" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J53" s="17" t="inlineStr">
+      <c r="K53" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L53" s="19" t="n">
+      <c r="M53" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M53" s="15" t="inlineStr">
+      <c r="N53" s="15" t="inlineStr">
         <is>
           <t>計画策定業務設計書 第4章（02_キックオフ・業務計画）</t>
         </is>
       </c>
-      <c r="N53" s="15" t="inlineStr">
+      <c r="O53" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -5995,48 +7165,53 @@
           <t>意見提出期間1か月</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
+      <c r="H54" s="16" t="inlineStr">
         <is>
           <t>町</t>
         </is>
       </c>
-      <c r="H54" s="16" t="inlineStr">
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="I54" s="16" t="inlineStr">
+      <c r="J54" s="16" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="J54" s="20" t="inlineStr">
+      <c r="K54" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K54" s="18" t="n">
+      <c r="L54" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="19" t="n">
+      <c r="M54" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M54" s="15" t="inlineStr">
+      <c r="N54" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N54" s="15" t="inlineStr">
+      <c r="O54" s="15" t="inlineStr">
         <is>
           <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
@@ -6063,48 +7238,53 @@
           <t>意見の整理、対応案の作成、計画への反映</t>
         </is>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F55" s="15" t="inlineStr">
+      <c r="G55" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="H55" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H55" s="16" t="inlineStr">
+      <c r="I55" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I55" s="16" t="inlineStr">
+      <c r="J55" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J55" s="20" t="inlineStr">
+      <c r="K55" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K55" s="18" t="n">
+      <c r="L55" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L55" s="19" t="n">
+      <c r="M55" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M55" s="15" t="inlineStr">
+      <c r="N55" s="15" t="inlineStr">
         <is>
           <t>対応表の様式は作成済み</t>
         </is>
       </c>
-      <c r="N55" s="15" t="inlineStr">
+      <c r="O55" s="15" t="inlineStr">
         <is>
           <t>パブコメの実施</t>
         </is>
@@ -6131,48 +7311,53 @@
           <t>最終案の確認</t>
         </is>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>B8 協議会・パブリックコメントの支援</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>仕様書4(5)</t>
         </is>
       </c>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="G56" s="15" t="inlineStr">
         <is>
           <t>【4(5)】高齢者福祉サービス推進協議会、パブリックコメントの支援。小野町高齢者福祉サービス推進協議会の開催及びパブリックコメントの実施について、資料の作成と運営・実施の支援を行うものとする。</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H56" s="16" t="inlineStr">
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I56" s="16" t="inlineStr">
+      <c r="J56" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J56" s="20" t="inlineStr">
+      <c r="K56" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K56" s="18" t="n">
+      <c r="L56" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L56" s="19" t="n">
+      <c r="M56" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M56" s="15" t="inlineStr">
+      <c r="N56" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N56" s="15" t="inlineStr">
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>意見への対応</t>
         </is>
@@ -6199,48 +7384,53 @@
           <t>パブリックコメント対応後の原稿</t>
         </is>
       </c>
-      <c r="E57" s="16" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>B7 最終調整及び計画書の作成</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>仕様書4(4)</t>
         </is>
       </c>
-      <c r="F57" s="15" t="inlineStr">
+      <c r="G57" s="15" t="inlineStr">
         <is>
           <t>【4(4)】最終調整及び計画書の作成・取りまとめ。（1）から（3）の結果を踏まえ、小野町高齢者保健福祉計画・第10期介護保険事業計画書を作成するものとする。</t>
         </is>
       </c>
-      <c r="G57" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H57" s="16" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I57" s="16" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J57" s="20" t="inlineStr">
+      <c r="K57" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K57" s="18" t="n">
+      <c r="L57" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="19" t="n">
+      <c r="M57" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M57" s="15" t="inlineStr">
+      <c r="N57" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N57" s="15" t="inlineStr">
+      <c r="O57" s="15" t="inlineStr">
         <is>
           <t>意見への対応</t>
         </is>
@@ -6267,48 +7457,53 @@
           <t>A4・4色刷り・80頁程度</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑤</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="G58" s="15" t="inlineStr">
         <is>
           <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
         </is>
       </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H58" s="16" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I58" s="16" t="inlineStr">
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J58" s="20" t="inlineStr">
+      <c r="K58" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K58" s="18" t="n">
+      <c r="L58" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="19" t="n">
+      <c r="M58" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="M58" s="15" t="inlineStr">
+      <c r="N58" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N58" s="15" t="inlineStr">
+      <c r="O58" s="15" t="inlineStr">
         <is>
           <t>原稿の確定</t>
         </is>
@@ -6335,48 +7530,53 @@
           <t>町の確認を経て校了</t>
         </is>
       </c>
-      <c r="E59" s="16" t="inlineStr">
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑤</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr">
+      <c r="G59" s="15" t="inlineStr">
         <is>
           <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="H59" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H59" s="16" t="inlineStr">
+      <c r="I59" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I59" s="16" t="inlineStr">
+      <c r="J59" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="J59" s="20" t="inlineStr">
+      <c r="K59" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K59" s="18" t="n">
+      <c r="L59" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L59" s="19" t="n">
+      <c r="M59" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M59" s="15" t="inlineStr">
+      <c r="N59" s="15" t="inlineStr">
         <is>
           <t>**逆算表を作成済み（令和9年2月下旬の校了が動かせない期限）**</t>
         </is>
       </c>
-      <c r="N59" s="15" t="inlineStr">
+      <c r="O59" s="15" t="inlineStr">
         <is>
           <t>組版</t>
         </is>
@@ -6403,48 +7603,53 @@
           <t>A4・4色刷り・8頁のページ割り</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑥</t>
         </is>
       </c>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="G60" s="15" t="inlineStr">
         <is>
           <t>【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="H60" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H60" s="16" t="inlineStr">
+      <c r="I60" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="I60" s="16" t="inlineStr">
+      <c r="J60" s="16" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="J60" s="17" t="inlineStr">
+      <c r="K60" s="17" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="K60" s="18" t="n">
+      <c r="L60" s="18" t="n">
         <v>100</v>
       </c>
-      <c r="L60" s="19" t="n">
+      <c r="M60" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M60" s="15" t="inlineStr">
+      <c r="N60" s="15" t="inlineStr">
         <is>
           <t>計画策定業務設計書 第2章（02_キックオフ・業務計画）</t>
         </is>
       </c>
-      <c r="N60" s="15" t="inlineStr">
+      <c r="O60" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -6471,48 +7676,53 @@
           <t>計画書からの抽出とリライト、図表8点程度</t>
         </is>
       </c>
-      <c r="E61" s="16" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑥</t>
         </is>
       </c>
-      <c r="F61" s="15" t="inlineStr">
+      <c r="G61" s="15" t="inlineStr">
         <is>
           <t>【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H61" s="16" t="inlineStr">
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="I61" s="16" t="inlineStr">
+      <c r="J61" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J61" s="20" t="inlineStr">
+      <c r="K61" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K61" s="18" t="n">
+      <c r="L61" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="19" t="n">
+      <c r="M61" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M61" s="15" t="inlineStr">
+      <c r="N61" s="15" t="inlineStr">
         <is>
           <t>構成案は作成済み</t>
         </is>
       </c>
-      <c r="N61" s="15" t="inlineStr">
+      <c r="O61" s="15" t="inlineStr">
         <is>
           <t>計画書の確定</t>
         </is>
@@ -6539,49 +7749,54 @@
           <t>計画書50部、概要版50部。色校正を含む</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品⑤・仕様書4 成果品⑥</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="G62" s="15" t="inlineStr">
         <is>
           <t>【成果品⑤】（5）小野町高齢者保健福祉計画・第10期介護保険事業計画　※データ（CD-R）1部、計画書印刷50部＜仕様＞A4版、4色刷り、80頁程度
 【成果品⑥】（6）小野町高齢者保健福祉計画・第10期介護保険事業計画概要版　※データ（CD-R）1部、概要版印刷50部＜仕様＞A4版、4色刷り、8頁</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H62" s="16" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I62" s="16" t="inlineStr">
+      <c r="J62" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J62" s="20" t="inlineStr">
+      <c r="K62" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K62" s="18" t="n">
+      <c r="L62" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L62" s="19" t="n">
+      <c r="M62" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="N62" s="15" t="inlineStr">
         <is>
           <t>**逆算表を作成済み。12月までに印刷業者を押さえる必要がある**</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr">
+      <c r="O62" s="15" t="inlineStr">
         <is>
           <t>校了</t>
         </is>
@@ -6608,48 +7823,53 @@
           <t>成果品①〜⑥のデータ</t>
         </is>
       </c>
-      <c r="E63" s="16" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>B9 成果品の納品</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>仕様書4 成果品</t>
         </is>
       </c>
-      <c r="F63" s="15" t="inlineStr">
+      <c r="G63" s="15" t="inlineStr">
         <is>
           <t>【成果品】（1）〜（4）のデータ（CD-R）1部、冊子（簡易製本）各3部／（5）（6）のデータ（CD-R）1部、計画書印刷50部／概要版印刷50部</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
         <is>
           <t>受託者</t>
         </is>
       </c>
-      <c r="H63" s="16" t="inlineStr">
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I63" s="16" t="inlineStr">
+      <c r="J63" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J63" s="20" t="inlineStr">
+      <c r="K63" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K63" s="18" t="n">
+      <c r="L63" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L63" s="19" t="n">
+      <c r="M63" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M63" s="15" t="inlineStr">
+      <c r="N63" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N63" s="15" t="inlineStr">
+      <c r="O63" s="15" t="inlineStr">
         <is>
           <t>各成果品の確定</t>
         </is>
@@ -6676,56 +7896,61 @@
           <t>令和9年3月31日まで</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>B10 業務管理・計画の基本的な考え方</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>仕様書3（業務期間）</t>
         </is>
       </c>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="G64" s="15" t="inlineStr">
         <is>
           <t>【3】契約締結の日から令和9年3月31日まで</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
         <is>
           <t>受託者・町</t>
         </is>
       </c>
-      <c r="H64" s="16" t="inlineStr">
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="I64" s="16" t="inlineStr">
+      <c r="J64" s="16" t="inlineStr">
         <is>
           <t>2027-03</t>
         </is>
       </c>
-      <c r="J64" s="20" t="inlineStr">
+      <c r="K64" s="20" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="K64" s="18" t="n">
+      <c r="L64" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="19" t="n">
+      <c r="M64" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M64" s="15" t="inlineStr">
+      <c r="N64" s="15" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="N64" s="15" t="inlineStr">
+      <c r="O64" s="15" t="inlineStr">
         <is>
           <t>全成果品の完成</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N64"/>
-  <conditionalFormatting sqref="K2:K64">
+  <autoFilter ref="A1:O64"/>
+  <conditionalFormatting sqref="L2:L64">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>100</formula>
     </cfRule>
@@ -6734,10 +7959,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J2:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,進行中,要対応,データ待ち,未着手"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="L2:L64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
@@ -6836,27 +8061,27 @@
         <v/>
       </c>
       <c r="C2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G2" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A2,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H2" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A2)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I2" s="16" t="inlineStr">
@@ -6886,27 +8111,27 @@
         <v/>
       </c>
       <c r="C3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G3" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A3,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H3" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A3)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I3" s="16" t="inlineStr">
@@ -6936,27 +8161,27 @@
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A4,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H4" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A4)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I4" s="16" t="inlineStr">
@@ -6986,27 +8211,27 @@
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A5,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H5" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A5)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I5" s="16" t="inlineStr">
@@ -7036,27 +8261,27 @@
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A6,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H6" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A6)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I6" s="16" t="inlineStr">
@@ -7086,27 +8311,27 @@
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A7,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H7" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A7)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I7" s="16" t="inlineStr">
@@ -7136,27 +8361,27 @@
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A8,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H8" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A8)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I8" s="16" t="inlineStr">
@@ -7186,27 +8411,27 @@
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A9,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H9" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A9)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I9" s="16" t="inlineStr">
@@ -7236,27 +8461,27 @@
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A10,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H10" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A10)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I10" s="16" t="inlineStr">
@@ -7286,27 +8511,27 @@
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"完了")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"完了")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"進行中")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"進行中")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"要対応")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"要対応")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"データ待ち")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"データ待ち")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$J$2:$J$64,"未着手")</f>
+        <f>COUNTIFS('01_WBS'!$A$2:$A$64,$A11,'01_WBS'!$K$2:$K$64,"未着手")</f>
         <v/>
       </c>
       <c r="H11" s="23">
-        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$K$2:$K$64*'01_WBS'!$L$2:$L$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$L$2:$L$64*'01_WBS'!$M$2:$M$64)/SUMPRODUCT(('01_WBS'!$A$2:$A$64=$A11)*'01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I11" s="16" t="inlineStr">
@@ -7356,7 +8581,7 @@
         <v/>
       </c>
       <c r="H12" s="26">
-        <f>IF(SUM('01_WBS'!$L$2:$L$64)=0,0,SUMPRODUCT('01_WBS'!$K$2:$K$64,'01_WBS'!$L$2:$L$64)/SUM('01_WBS'!$L$2:$L$64)/100)</f>
+        <f>IF(SUM('01_WBS'!$M$2:$M$64)=0,0,SUMPRODUCT('01_WBS'!$L$2:$L$64,'01_WBS'!$M$2:$M$64)/SUM('01_WBS'!$M$2:$M$64)/100)</f>
         <v/>
       </c>
       <c r="I12" s="16" t="inlineStr">
